--- a/data/theo_doi_vi.xlsx
+++ b/data/theo_doi_vi.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
     <numFmt numFmtId="165" formatCode="+#,##0.####;-#,##0.####;0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,16 @@
     <font>
       <name val="Arial"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +57,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -91,6 +111,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -458,13 +484,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +516,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -504,6 +542,12 @@
         <v>6254146.877</v>
       </c>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>6238546.7092</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>-15600.1678</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -520,6 +564,12 @@
         <v>4593414.2832</v>
       </c>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>4593414.2832</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -536,6 +586,12 @@
         <v>4032682.9341</v>
       </c>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>4032682.9341</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -552,6 +608,12 @@
         <v>4000000</v>
       </c>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -568,6 +630,12 @@
         <v>3663634.4136</v>
       </c>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>3663634.4136</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -584,6 +652,12 @@
         <v>3628524.82</v>
       </c>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>3628524.82</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -600,6 +674,12 @@
         <v>2743926.9899</v>
       </c>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>2743926.9899</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -616,6 +696,12 @@
         <v>2407572.5386</v>
       </c>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>2407572.5386</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -632,6 +718,12 @@
         <v>2000000.0012</v>
       </c>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>2000000.0012</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -648,6 +740,12 @@
         <v>2000000</v>
       </c>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -664,6 +762,12 @@
         <v>1938773.4789</v>
       </c>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>1938773.4789</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -680,6 +784,12 @@
         <v>1810914.2302</v>
       </c>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>1810914.2302</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -696,6 +806,12 @@
         <v>1663791.3571</v>
       </c>
       <c r="D14" s="5" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>1663791.3571</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -712,6 +828,12 @@
         <v>1501314.8913</v>
       </c>
       <c r="D15" s="5" t="n"/>
+      <c r="E15" s="4" t="n">
+        <v>1501314.8913</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -728,6 +850,12 @@
         <v>1236777.8944</v>
       </c>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="4" t="n">
+        <v>1236777.8944</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -744,6 +872,12 @@
         <v>1200000</v>
       </c>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -760,6 +894,12 @@
         <v>1178546.0449</v>
       </c>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>1178546.0449</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -776,6 +916,12 @@
         <v>1173068.8403</v>
       </c>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>1173068.8403</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -792,6 +938,12 @@
         <v>1075254.7301</v>
       </c>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="4" t="n">
+        <v>1075254.7301</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -808,6 +960,12 @@
         <v>1070173.9749</v>
       </c>
       <c r="D21" s="5" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>1070173.9749</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -824,6 +982,12 @@
         <v>1030000</v>
       </c>
       <c r="D22" s="5" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -840,6 +1004,12 @@
         <v>1027286.3894</v>
       </c>
       <c r="D23" s="5" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>1027286.3894</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -856,6 +1026,12 @@
         <v>1023082.1439</v>
       </c>
       <c r="D24" s="5" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>1023082.1439</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -872,6 +1048,12 @@
         <v>1012395.8946</v>
       </c>
       <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n">
+        <v>1012395.8946</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -888,6 +1070,12 @@
         <v>1009987.2763</v>
       </c>
       <c r="D26" s="5" t="n"/>
+      <c r="E26" s="4" t="n">
+        <v>1009987.2763</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -904,6 +1092,12 @@
         <v>1006825.8922</v>
       </c>
       <c r="D27" s="5" t="n"/>
+      <c r="E27" s="4" t="n">
+        <v>1006825.8922</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -920,6 +1114,12 @@
         <v>1000000</v>
       </c>
       <c r="D28" s="5" t="n"/>
+      <c r="E28" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -936,6 +1136,12 @@
         <v>1000000</v>
       </c>
       <c r="D29" s="5" t="n"/>
+      <c r="E29" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -952,6 +1158,12 @@
         <v>998014.552</v>
       </c>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="4" t="n">
+        <v>998014.552</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -968,6 +1180,12 @@
         <v>990000</v>
       </c>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="4" t="n">
+        <v>990000</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -984,6 +1202,12 @@
         <v>979187.2334</v>
       </c>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="4" t="n">
+        <v>979187.2334</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1000,6 +1224,12 @@
         <v>889548.5399</v>
       </c>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="4" t="n">
+        <v>889548.5399</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1016,6 +1246,12 @@
         <v>887524.782</v>
       </c>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="4" t="n">
+        <v>887524.782</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1032,6 +1268,12 @@
         <v>879501.0418</v>
       </c>
       <c r="D35" s="5" t="n"/>
+      <c r="E35" s="4" t="n">
+        <v>879501.0418</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1048,6 +1290,12 @@
         <v>862367.0839</v>
       </c>
       <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="n">
+        <v>862367.0839</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1064,6 +1312,12 @@
         <v>838549.1449</v>
       </c>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="n">
+        <v>838549.1449</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1080,6 +1334,12 @@
         <v>836992.2512000001</v>
       </c>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="4" t="n">
+        <v>836992.2512000001</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1096,6 +1356,12 @@
         <v>834355.5257</v>
       </c>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="4" t="n">
+        <v>834355.5257</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1112,6 +1378,12 @@
         <v>823353.5943</v>
       </c>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n">
+        <v>823353.5943</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1128,6 +1400,12 @@
         <v>809555.4168</v>
       </c>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n">
+        <v>809555.4168</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1144,6 +1422,12 @@
         <v>799900.5672</v>
       </c>
       <c r="D42" s="5" t="n"/>
+      <c r="E42" s="4" t="n">
+        <v>799900.5672</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1160,6 +1444,12 @@
         <v>763127.9248</v>
       </c>
       <c r="D43" s="5" t="n"/>
+      <c r="E43" s="4" t="n">
+        <v>763127.9248</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1176,6 +1466,12 @@
         <v>747868.0344</v>
       </c>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="4" t="n">
+        <v>747868.0344</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1192,6 +1488,12 @@
         <v>732703.1313</v>
       </c>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="4" t="n">
+        <v>732703.1313</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1208,6 +1510,12 @@
         <v>725096.5494</v>
       </c>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="n">
+        <v>725096.5494</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1224,6 +1532,12 @@
         <v>711759.0045</v>
       </c>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="n">
+        <v>711759.0045</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1240,6 +1554,12 @@
         <v>693657.6485</v>
       </c>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="4" t="n">
+        <v>693657.6485</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1256,6 +1576,12 @@
         <v>672356.3260999999</v>
       </c>
       <c r="D49" s="5" t="n"/>
+      <c r="E49" s="4" t="n">
+        <v>672356.3260999999</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1272,6 +1598,12 @@
         <v>645576.1191</v>
       </c>
       <c r="D50" s="5" t="n"/>
+      <c r="E50" s="4" t="n">
+        <v>645576.1191</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1288,6 +1620,12 @@
         <v>645051.7397</v>
       </c>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n">
+        <v>645051.7397</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1304,6 +1642,12 @@
         <v>634607.2181000001</v>
       </c>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>634607.2181000001</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1320,6 +1664,12 @@
         <v>620661.4845</v>
       </c>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="4" t="n">
+        <v>620661.4845</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1336,6 +1686,12 @@
         <v>618815.814</v>
       </c>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="4" t="n">
+        <v>618815.814</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1352,6 +1708,12 @@
         <v>577999.0600000001</v>
       </c>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="4" t="n">
+        <v>577999.0600000001</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1368,6 +1730,12 @@
         <v>574396.1581</v>
       </c>
       <c r="D56" s="5" t="n"/>
+      <c r="E56" s="4" t="n">
+        <v>574396.1581</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1384,6 +1752,12 @@
         <v>543641.1091999999</v>
       </c>
       <c r="D57" s="5" t="n"/>
+      <c r="E57" s="4" t="n">
+        <v>543641.1091999999</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1400,6 +1774,12 @@
         <v>540799.1483999999</v>
       </c>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="4" t="n">
+        <v>540799.1483999999</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1416,6 +1796,12 @@
         <v>522769.5865</v>
       </c>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="4" t="n">
+        <v>522769.5865</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1432,6 +1818,12 @@
         <v>514620.6938</v>
       </c>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="4" t="n">
+        <v>514620.6938</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1448,6 +1840,12 @@
         <v>502486.445</v>
       </c>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="4" t="n">
+        <v>502486.445</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1464,6 +1862,12 @@
         <v>500000.0059</v>
       </c>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="4" t="n">
+        <v>500000.0059</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1480,6 +1884,12 @@
         <v>496416.2686</v>
       </c>
       <c r="D63" s="5" t="n"/>
+      <c r="E63" s="4" t="n">
+        <v>496416.2686</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1496,6 +1906,12 @@
         <v>493196.1109</v>
       </c>
       <c r="D64" s="5" t="n"/>
+      <c r="E64" s="4" t="n">
+        <v>493196.1109</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1512,6 +1928,12 @@
         <v>492785.4309</v>
       </c>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="4" t="n">
+        <v>492785.4309</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1528,6 +1950,12 @@
         <v>485670.7376</v>
       </c>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>485670.7376</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1544,6 +1972,12 @@
         <v>479895.4935</v>
       </c>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="4" t="n">
+        <v>479895.4935</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1560,6 +1994,12 @@
         <v>478481.1661</v>
       </c>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="4" t="n">
+        <v>478481.1661</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1576,6 +2016,12 @@
         <v>475707.078</v>
       </c>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="4" t="n">
+        <v>475707.078</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1592,6 +2038,12 @@
         <v>464907.3106</v>
       </c>
       <c r="D70" s="5" t="n"/>
+      <c r="E70" s="4" t="n">
+        <v>464907.3106</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1608,6 +2060,12 @@
         <v>456856.3119</v>
       </c>
       <c r="D71" s="5" t="n"/>
+      <c r="E71" s="4" t="n">
+        <v>456856.3119</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1624,6 +2082,12 @@
         <v>450737.5206</v>
       </c>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="4" t="n">
+        <v>450737.5206</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1640,6 +2104,12 @@
         <v>406654.2213</v>
       </c>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="4" t="n">
+        <v>406654.2213</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1656,6 +2126,12 @@
         <v>391965.0651</v>
       </c>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="4" t="n">
+        <v>391965.0651</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -1672,6 +2148,12 @@
         <v>373610.2211</v>
       </c>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="4" t="n">
+        <v>373610.2211</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1688,6 +2170,12 @@
         <v>372035.7101</v>
       </c>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="4" t="n">
+        <v>372035.7101</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -1704,6 +2192,12 @@
         <v>368779.171</v>
       </c>
       <c r="D77" s="5" t="n"/>
+      <c r="E77" s="4" t="n">
+        <v>368779.171</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1720,6 +2214,12 @@
         <v>364313.8869</v>
       </c>
       <c r="D78" s="5" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>364313.8869</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -1736,6 +2236,12 @@
         <v>349130.2568</v>
       </c>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>349130.2568</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1752,6 +2258,12 @@
         <v>317618.675</v>
       </c>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="4" t="n">
+        <v>317618.675</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -1768,6 +2280,12 @@
         <v>306593.6026</v>
       </c>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>306593.6026</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1784,6 +2302,12 @@
         <v>304779.1145</v>
       </c>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>304779.1145</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -1800,6 +2324,12 @@
         <v>279571.178</v>
       </c>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="4" t="n">
+        <v>279571.178</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1816,6 +2346,12 @@
         <v>276846.4217</v>
       </c>
       <c r="D84" s="5" t="n"/>
+      <c r="E84" s="4" t="n">
+        <v>276846.4217</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -1832,6 +2368,12 @@
         <v>270452.3185</v>
       </c>
       <c r="D85" s="5" t="n"/>
+      <c r="E85" s="4" t="n">
+        <v>270452.3185</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1848,6 +2390,12 @@
         <v>265595.8775</v>
       </c>
       <c r="D86" s="5" t="n"/>
+      <c r="E86" s="4" t="n">
+        <v>265595.8775</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -1864,6 +2412,12 @@
         <v>262311.5799</v>
       </c>
       <c r="D87" s="5" t="n"/>
+      <c r="E87" s="4" t="n">
+        <v>262311.5799</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -1880,6 +2434,12 @@
         <v>253086.7083</v>
       </c>
       <c r="D88" s="5" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>253086.7083</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -1896,6 +2456,12 @@
         <v>248683.7198</v>
       </c>
       <c r="D89" s="5" t="n"/>
+      <c r="E89" s="4" t="n">
+        <v>248683.7198</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -1912,6 +2478,12 @@
         <v>245600</v>
       </c>
       <c r="D90" s="5" t="n"/>
+      <c r="E90" s="4" t="n">
+        <v>245600</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -1928,6 +2500,12 @@
         <v>234392.5508</v>
       </c>
       <c r="D91" s="5" t="n"/>
+      <c r="E91" s="4" t="n">
+        <v>234392.5508</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1944,6 +2522,12 @@
         <v>232105.4869</v>
       </c>
       <c r="D92" s="5" t="n"/>
+      <c r="E92" s="4" t="n">
+        <v>232105.4869</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -1960,6 +2544,12 @@
         <v>232010.2351</v>
       </c>
       <c r="D93" s="5" t="n"/>
+      <c r="E93" s="4" t="n">
+        <v>232010.2351</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -1976,6 +2566,12 @@
         <v>210417.5518</v>
       </c>
       <c r="D94" s="5" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>210417.5518</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -1992,6 +2588,12 @@
         <v>208196.4767</v>
       </c>
       <c r="D95" s="5" t="n"/>
+      <c r="E95" s="4" t="n">
+        <v>208196.4767</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2008,6 +2610,12 @@
         <v>200680.3037</v>
       </c>
       <c r="D96" s="5" t="n"/>
+      <c r="E96" s="4" t="n">
+        <v>200680.3037</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2024,6 +2632,12 @@
         <v>200000</v>
       </c>
       <c r="D97" s="5" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2040,6 +2654,12 @@
         <v>193698.4706</v>
       </c>
       <c r="D98" s="5" t="n"/>
+      <c r="E98" s="4" t="n">
+        <v>193698.4706</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2056,6 +2676,12 @@
         <v>189214.5731</v>
       </c>
       <c r="D99" s="5" t="n"/>
+      <c r="E99" s="4" t="n">
+        <v>189214.5731</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2072,6 +2698,12 @@
         <v>184057.6874</v>
       </c>
       <c r="D100" s="5" t="n"/>
+      <c r="E100" s="4" t="n">
+        <v>184057.6874</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2088,6 +2720,12 @@
         <v>179226.4255</v>
       </c>
       <c r="D101" s="5" t="n"/>
+      <c r="E101" s="4" t="n">
+        <v>179226.4255</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2100,13 +2738,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2130,6 +2770,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2146,6 +2796,12 @@
         <v>27004519.2645</v>
       </c>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>27004519.2645</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2162,6 +2818,12 @@
         <v>26470000</v>
       </c>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>26470000</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2178,6 +2840,12 @@
         <v>23480366.3071</v>
       </c>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>23480366.3071</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2194,6 +2862,12 @@
         <v>23069630.0654</v>
       </c>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>23069630.0654</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2210,6 +2884,12 @@
         <v>21968454.2781</v>
       </c>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>22585099.5716</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>616645.2935</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2906,12 @@
         <v>20000000.0069</v>
       </c>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>20000000.0069</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2242,6 +2928,12 @@
         <v>18754869.6112</v>
       </c>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>18754869.6112</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2258,6 +2950,12 @@
         <v>17900000</v>
       </c>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>17900000</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2274,6 +2972,12 @@
         <v>16000000</v>
       </c>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2290,6 +2994,12 @@
         <v>15566890.7147</v>
       </c>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>15566890.7147</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2306,6 +3016,12 @@
         <v>15077130.0016</v>
       </c>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>15077130.0016</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2322,6 +3038,12 @@
         <v>14000000.0458</v>
       </c>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>14000000.0458</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2338,6 +3060,12 @@
         <v>13946038.6243</v>
       </c>
       <c r="D14" s="5" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>13946038.6243</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2354,6 +3082,12 @@
         <v>13561030.1654</v>
       </c>
       <c r="D15" s="5" t="n"/>
+      <c r="E15" s="4" t="n">
+        <v>13561030.1654</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2370,6 +3104,12 @@
         <v>13000000</v>
       </c>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="4" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2386,6 +3126,12 @@
         <v>12877042.1771</v>
       </c>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>12877042.1771</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2402,6 +3148,12 @@
         <v>12076398.0324</v>
       </c>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>12076398.0324</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2418,6 +3170,12 @@
         <v>12035369.0946</v>
       </c>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>12035369.0946</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2434,6 +3192,12 @@
         <v>11000100</v>
       </c>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="4" t="n">
+        <v>11000100</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2450,6 +3214,12 @@
         <v>10537438.7702</v>
       </c>
       <c r="D21" s="5" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>10537438.7702</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2466,6 +3236,12 @@
         <v>10300500</v>
       </c>
       <c r="D22" s="5" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>9100000</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-1200500</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2482,6 +3258,12 @@
         <v>10145020.9338</v>
       </c>
       <c r="D23" s="5" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>10145020.9338</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2498,6 +3280,12 @@
         <v>10064319.802</v>
       </c>
       <c r="D24" s="5" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>10064319.802</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2514,6 +3302,12 @@
         <v>10050792.1674</v>
       </c>
       <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n">
+        <v>10050792.1674</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2530,6 +3324,12 @@
         <v>9974153.375</v>
       </c>
       <c r="D26" s="5" t="n"/>
+      <c r="E26" s="4" t="n">
+        <v>9974153.375</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2546,6 +3346,12 @@
         <v>9950177.2448</v>
       </c>
       <c r="D27" s="5" t="n"/>
+      <c r="E27" s="4" t="n">
+        <v>9950177.2448</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2562,6 +3368,12 @@
         <v>9450000</v>
       </c>
       <c r="D28" s="5" t="n"/>
+      <c r="E28" s="4" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2578,6 +3390,12 @@
         <v>8928368.352</v>
       </c>
       <c r="D29" s="5" t="n"/>
+      <c r="E29" s="4" t="n">
+        <v>8928368.352</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2594,6 +3412,12 @@
         <v>8652441.2765</v>
       </c>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="4" t="n">
+        <v>8652441.2765</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2610,6 +3434,12 @@
         <v>8363455.9946</v>
       </c>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="4" t="n">
+        <v>8363455.9946</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2626,6 +3456,12 @@
         <v>8023815.4821</v>
       </c>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="4" t="n">
+        <v>8023815.4821</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2642,6 +3478,12 @@
         <v>8023361.3442</v>
       </c>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="4" t="n">
+        <v>8023361.3442</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2658,6 +3500,12 @@
         <v>8000005.5172</v>
       </c>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="4" t="n">
+        <v>8000005.5172</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2674,6 +3522,12 @@
         <v>7000187</v>
       </c>
       <c r="D35" s="5" t="n"/>
+      <c r="E35" s="4" t="n">
+        <v>7000187</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2690,6 +3544,12 @@
         <v>6936249.5374</v>
       </c>
       <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="n">
+        <v>6936249.5374</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2706,6 +3566,12 @@
         <v>6850000.7835</v>
       </c>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="n">
+        <v>6850000.7835</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2722,6 +3588,12 @@
         <v>6500000</v>
       </c>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2738,6 +3610,12 @@
         <v>6434508.4673</v>
       </c>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="4" t="n">
+        <v>6434508.4673</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2754,6 +3632,12 @@
         <v>6157877.2306</v>
       </c>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n">
+        <v>6157877.2306</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2770,6 +3654,12 @@
         <v>5674606.3075</v>
       </c>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n">
+        <v>5674606.3075</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2786,6 +3676,12 @@
         <v>5565141.3215</v>
       </c>
       <c r="D42" s="5" t="n"/>
+      <c r="E42" s="4" t="n">
+        <v>5565141.3215</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2802,6 +3698,12 @@
         <v>5537959.6635</v>
       </c>
       <c r="D43" s="5" t="n"/>
+      <c r="E43" s="4" t="n">
+        <v>5537959.6635</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2818,6 +3720,12 @@
         <v>5443778.7854</v>
       </c>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="4" t="n">
+        <v>5443778.7854</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2834,6 +3742,12 @@
         <v>5249101.3481</v>
       </c>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="4" t="n">
+        <v>5249101.3481</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2850,6 +3764,12 @@
         <v>5246809.5221</v>
       </c>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="n">
+        <v>5246809.5221</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2866,6 +3786,12 @@
         <v>5229000</v>
       </c>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="n">
+        <v>5229000</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2882,6 +3808,12 @@
         <v>5188888.88</v>
       </c>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="4" t="n">
+        <v>5188888.88</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2898,6 +3830,12 @@
         <v>5003000</v>
       </c>
       <c r="D49" s="5" t="n"/>
+      <c r="E49" s="4" t="n">
+        <v>5003000</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2914,6 +3852,12 @@
         <v>5000000.0018</v>
       </c>
       <c r="D50" s="5" t="n"/>
+      <c r="E50" s="4" t="n">
+        <v>5000000.0018</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2930,6 +3874,12 @@
         <v>4664770.6328</v>
       </c>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n">
+        <v>4664770.6328</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2946,6 +3896,12 @@
         <v>4614481.0346</v>
       </c>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>4614481.0346</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2962,6 +3918,12 @@
         <v>4540406.5588</v>
       </c>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="4" t="n">
+        <v>4540406.5588</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2978,6 +3940,12 @@
         <v>4537210.2091</v>
       </c>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="4" t="n">
+        <v>4537210.2091</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2994,6 +3962,12 @@
         <v>4521268.8043</v>
       </c>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="4" t="n">
+        <v>4521268.8043</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3010,6 +3984,12 @@
         <v>4519500</v>
       </c>
       <c r="D56" s="5" t="n"/>
+      <c r="E56" s="4" t="n">
+        <v>4519500</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3026,6 +4006,12 @@
         <v>4426640.2635</v>
       </c>
       <c r="D57" s="5" t="n"/>
+      <c r="E57" s="4" t="n">
+        <v>4426640.2635</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3042,6 +4028,12 @@
         <v>4065312.1229</v>
       </c>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="4" t="n">
+        <v>4065312.1229</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3058,6 +4050,12 @@
         <v>4044917.9442</v>
       </c>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="4" t="n">
+        <v>4044917.9442</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3074,6 +4072,12 @@
         <v>4000014.4373</v>
       </c>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="4" t="n">
+        <v>4000014.4373</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3090,6 +4094,12 @@
         <v>3927600.0561</v>
       </c>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="4" t="n">
+        <v>3927600.0561</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3106,6 +4116,12 @@
         <v>3891798.8644</v>
       </c>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="4" t="n">
+        <v>3891798.8644</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3122,6 +4138,12 @@
         <v>3806790</v>
       </c>
       <c r="D63" s="5" t="n"/>
+      <c r="E63" s="4" t="n">
+        <v>3806790</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3138,6 +4160,12 @@
         <v>3777387</v>
       </c>
       <c r="D64" s="5" t="n"/>
+      <c r="E64" s="4" t="n">
+        <v>3777387</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3154,6 +4182,12 @@
         <v>3710432.1672</v>
       </c>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="4" t="n">
+        <v>3710432.1672</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3170,6 +4204,12 @@
         <v>3670420</v>
       </c>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>3670420</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3186,6 +4226,12 @@
         <v>3651821.6602</v>
       </c>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="4" t="n">
+        <v>3651821.6602</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3202,6 +4248,12 @@
         <v>3579376.119</v>
       </c>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="4" t="n">
+        <v>3579376.119</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3218,6 +4270,12 @@
         <v>3534274.8743</v>
       </c>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="4" t="n">
+        <v>3534274.8743</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3234,6 +4292,12 @@
         <v>3500497.764</v>
       </c>
       <c r="D70" s="5" t="n"/>
+      <c r="E70" s="4" t="n">
+        <v>3500497.764</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3250,6 +4314,12 @@
         <v>3487322.2855</v>
       </c>
       <c r="D71" s="5" t="n"/>
+      <c r="E71" s="4" t="n">
+        <v>3487322.2855</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3266,6 +4336,12 @@
         <v>3399453.366</v>
       </c>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="4" t="n">
+        <v>3399453.366</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3282,6 +4358,12 @@
         <v>3287999.9796</v>
       </c>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="4" t="n">
+        <v>3287999.9796</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3298,6 +4380,12 @@
         <v>3277153.2544</v>
       </c>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="4" t="n">
+        <v>3277153.2544</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3314,6 +4402,12 @@
         <v>3217781.3694</v>
       </c>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="4" t="n">
+        <v>3217781.3694</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3330,6 +4424,12 @@
         <v>3203353.2229</v>
       </c>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="4" t="n">
+        <v>3203353.2229</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3346,6 +4446,12 @@
         <v>3148181.9096</v>
       </c>
       <c r="D77" s="5" t="n"/>
+      <c r="E77" s="4" t="n">
+        <v>3148181.9096</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3362,6 +4468,12 @@
         <v>3130293.0222</v>
       </c>
       <c r="D78" s="5" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>3130293.0222</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3378,6 +4490,12 @@
         <v>3100000</v>
       </c>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3394,6 +4512,12 @@
         <v>3032188.4799</v>
       </c>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="4" t="n">
+        <v>3032188.4799</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3410,6 +4534,12 @@
         <v>2856916.0402</v>
       </c>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>2856916.0402</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3426,6 +4556,12 @@
         <v>2728360.891</v>
       </c>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>2728360.891</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3442,6 +4578,12 @@
         <v>2646250.8473</v>
       </c>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="4" t="n">
+        <v>2646250.8473</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3458,6 +4600,12 @@
         <v>2603698.568</v>
       </c>
       <c r="D84" s="5" t="n"/>
+      <c r="E84" s="4" t="n">
+        <v>2603698.568</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3474,6 +4622,12 @@
         <v>2583083.2177</v>
       </c>
       <c r="D85" s="5" t="n"/>
+      <c r="E85" s="4" t="n">
+        <v>2585748.6673</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>2665.4496</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3490,6 +4644,12 @@
         <v>2578757.6772</v>
       </c>
       <c r="D86" s="5" t="n"/>
+      <c r="E86" s="4" t="n">
+        <v>2578757.6772</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3506,6 +4666,12 @@
         <v>2566060.4818</v>
       </c>
       <c r="D87" s="5" t="n"/>
+      <c r="E87" s="4" t="n">
+        <v>2566060.4818</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3522,6 +4688,12 @@
         <v>2500000</v>
       </c>
       <c r="D88" s="5" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3538,6 +4710,12 @@
         <v>2489000.3733</v>
       </c>
       <c r="D89" s="5" t="n"/>
+      <c r="E89" s="4" t="n">
+        <v>2489000.3733</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3554,6 +4732,12 @@
         <v>2470041.0495</v>
       </c>
       <c r="D90" s="5" t="n"/>
+      <c r="E90" s="4" t="n">
+        <v>2470041.0495</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3570,6 +4754,12 @@
         <v>2411374.8288</v>
       </c>
       <c r="D91" s="5" t="n"/>
+      <c r="E91" s="4" t="n">
+        <v>2411374.8288</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3586,6 +4776,12 @@
         <v>2384406.6695</v>
       </c>
       <c r="D92" s="5" t="n"/>
+      <c r="E92" s="4" t="n">
+        <v>2384406.6695</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3602,6 +4798,12 @@
         <v>2370068.8696</v>
       </c>
       <c r="D93" s="5" t="n"/>
+      <c r="E93" s="4" t="n">
+        <v>2370068.8696</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3618,6 +4820,12 @@
         <v>2361819.476</v>
       </c>
       <c r="D94" s="5" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>2361819.476</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3634,6 +4842,12 @@
         <v>2335954.4783</v>
       </c>
       <c r="D95" s="5" t="n"/>
+      <c r="E95" s="4" t="n">
+        <v>2335954.4783</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3650,6 +4864,12 @@
         <v>2289568.431</v>
       </c>
       <c r="D96" s="5" t="n"/>
+      <c r="E96" s="4" t="n">
+        <v>2289568.431</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3666,6 +4886,12 @@
         <v>2275539.2648</v>
       </c>
       <c r="D97" s="5" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>2275539.2648</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3682,6 +4908,12 @@
         <v>2264858.6935</v>
       </c>
       <c r="D98" s="5" t="n"/>
+      <c r="E98" s="4" t="n">
+        <v>2264858.6935</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3698,6 +4930,12 @@
         <v>2263684.8207</v>
       </c>
       <c r="D99" s="5" t="n"/>
+      <c r="E99" s="4" t="n">
+        <v>2263684.8207</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3714,6 +4952,12 @@
         <v>2227988.9889</v>
       </c>
       <c r="D100" s="5" t="n"/>
+      <c r="E100" s="4" t="n">
+        <v>2227988.9889</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3730,6 +4974,12 @@
         <v>2203811.7904</v>
       </c>
       <c r="D101" s="5" t="n"/>
+      <c r="E101" s="4" t="n">
+        <v>2203811.7904</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/theo_doi_vi.xlsx
+++ b/data/theo_doi_vi.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="DIDI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="YODA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UTYA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="REDO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -493,6 +495,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +530,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 16:11</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -548,6 +562,12 @@
       <c r="F2" s="6" t="n">
         <v>-15600.1678</v>
       </c>
+      <c r="G2" s="4" t="n">
+        <v>6195773.8658</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>-42772.8434</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -570,6 +590,12 @@
       <c r="F3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="4" t="n">
+        <v>4593414.2832</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -592,6 +618,12 @@
       <c r="F4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="4" t="n">
+        <v>4032682.9341</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -614,6 +646,12 @@
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -634,6 +672,12 @@
         <v>3663634.4136</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3663634.4136</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -656,6 +700,12 @@
         <v>3628524.82</v>
       </c>
       <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3628524.82</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -678,6 +728,12 @@
         <v>2743926.9899</v>
       </c>
       <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2743926.9899</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -700,6 +756,12 @@
         <v>2407572.5386</v>
       </c>
       <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2407572.5386</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -722,6 +784,12 @@
         <v>2000000.0012</v>
       </c>
       <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2000000.0012</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -746,6 +814,12 @@
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -768,6 +842,12 @@
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="4" t="n">
+        <v>1938773.4789</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -788,7 +868,13 @@
         <v>1810914.2302</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1840944.1019</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>30029.8717</v>
       </c>
     </row>
     <row r="14">
@@ -810,6 +896,12 @@
         <v>1663791.3571</v>
       </c>
       <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1663791.3571</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -834,6 +926,12 @@
       <c r="F15" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="4" t="n">
+        <v>1501314.8913</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -856,6 +954,12 @@
       <c r="F16" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="4" t="n">
+        <v>1236777.8944</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -878,6 +982,12 @@
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -898,6 +1008,12 @@
         <v>1178546.0449</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1178546.0449</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -922,6 +1038,12 @@
       <c r="F19" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="4" t="n">
+        <v>1173068.8403</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -944,6 +1066,12 @@
       <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="4" t="n">
+        <v>1075254.7301</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -966,6 +1094,12 @@
       <c r="F21" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G21" s="4" t="n">
+        <v>1070173.9749</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -988,6 +1122,12 @@
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="4" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1008,6 +1148,12 @@
         <v>1027286.3894</v>
       </c>
       <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1027286.3894</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1030,6 +1176,12 @@
         <v>1023082.1439</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1023082.1439</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1054,6 +1206,12 @@
       <c r="F25" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G25" s="4" t="n">
+        <v>1012395.8946</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1074,6 +1232,12 @@
         <v>1009987.2763</v>
       </c>
       <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1009987.2763</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1096,6 +1260,12 @@
         <v>1006825.8922</v>
       </c>
       <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1006825.8922</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1120,6 +1290,12 @@
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G28" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1142,6 +1318,12 @@
       <c r="F29" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G29" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1162,6 +1344,12 @@
         <v>998014.552</v>
       </c>
       <c r="F30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>998014.552</v>
+      </c>
+      <c r="H30" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1186,6 +1374,12 @@
       <c r="F31" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G31" s="4" t="n">
+        <v>990000</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1208,6 +1402,12 @@
       <c r="F32" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G32" s="4" t="n">
+        <v>979187.2334</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1228,6 +1428,12 @@
         <v>889548.5399</v>
       </c>
       <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>889548.5399</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1252,6 +1458,12 @@
       <c r="F34" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G34" s="4" t="n">
+        <v>887524.782</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1274,6 +1486,12 @@
       <c r="F35" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G35" s="4" t="n">
+        <v>879501.0418</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1294,6 +1512,12 @@
         <v>862367.0839</v>
       </c>
       <c r="F36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>862367.0839</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1316,6 +1540,12 @@
         <v>838549.1449</v>
       </c>
       <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>838549.1449</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1338,6 +1568,12 @@
         <v>836992.2512000001</v>
       </c>
       <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>836992.2512000001</v>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1362,6 +1598,12 @@
       <c r="F39" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G39" s="4" t="n">
+        <v>834355.5257</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1384,6 +1626,12 @@
       <c r="F40" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G40" s="4" t="n">
+        <v>823353.5943</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1406,6 +1654,12 @@
       <c r="F41" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G41" s="4" t="n">
+        <v>809555.4168</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1428,6 +1682,12 @@
       <c r="F42" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G42" s="4" t="n">
+        <v>799900.5672</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1450,6 +1710,12 @@
       <c r="F43" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G43" s="4" t="n">
+        <v>763127.9248</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1472,6 +1738,12 @@
       <c r="F44" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G44" s="4" t="n">
+        <v>747868.0344</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1492,6 +1764,12 @@
         <v>732703.1313</v>
       </c>
       <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>732703.1313</v>
+      </c>
+      <c r="H45" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1514,6 +1792,12 @@
         <v>725096.5494</v>
       </c>
       <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>725096.5494</v>
+      </c>
+      <c r="H46" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1536,6 +1820,12 @@
         <v>711759.0045</v>
       </c>
       <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>711759.0045</v>
+      </c>
+      <c r="H47" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1558,6 +1848,12 @@
         <v>693657.6485</v>
       </c>
       <c r="F48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>693657.6485</v>
+      </c>
+      <c r="H48" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1580,6 +1876,12 @@
         <v>672356.3260999999</v>
       </c>
       <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>672356.3260999999</v>
+      </c>
+      <c r="H49" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1604,6 +1906,12 @@
       <c r="F50" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G50" s="4" t="n">
+        <v>645576.1191</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1624,6 +1932,12 @@
         <v>645051.7397</v>
       </c>
       <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>645051.7397</v>
+      </c>
+      <c r="H51" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1648,6 +1962,12 @@
       <c r="F52" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G52" s="4" t="n">
+        <v>634607.2181000001</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1668,6 +1988,12 @@
         <v>620661.4845</v>
       </c>
       <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>620661.4845</v>
+      </c>
+      <c r="H53" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1692,6 +2018,12 @@
       <c r="F54" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G54" s="4" t="n">
+        <v>618815.814</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1714,6 +2046,12 @@
       <c r="F55" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G55" s="4" t="n">
+        <v>577999.0600000001</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1736,6 +2074,12 @@
       <c r="F56" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G56" s="4" t="n">
+        <v>574396.1581</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1758,6 +2102,12 @@
       <c r="F57" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G57" s="4" t="n">
+        <v>543641.1091999999</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1780,6 +2130,12 @@
       <c r="F58" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G58" s="4" t="n">
+        <v>540799.1483999999</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1802,6 +2158,12 @@
       <c r="F59" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G59" s="4" t="n">
+        <v>522769.5865</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1822,6 +2184,12 @@
         <v>514620.6938</v>
       </c>
       <c r="F60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>514620.6938</v>
+      </c>
+      <c r="H60" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1844,6 +2212,12 @@
         <v>502486.445</v>
       </c>
       <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>502486.445</v>
+      </c>
+      <c r="H61" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1866,6 +2240,12 @@
         <v>500000.0059</v>
       </c>
       <c r="F62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>500000.0059</v>
+      </c>
+      <c r="H62" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1888,6 +2268,12 @@
         <v>496416.2686</v>
       </c>
       <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>496416.2686</v>
+      </c>
+      <c r="H63" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1912,6 +2298,12 @@
       <c r="F64" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G64" s="4" t="n">
+        <v>493196.1109</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1934,6 +2326,12 @@
       <c r="F65" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G65" s="4" t="n">
+        <v>492785.4309</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1956,6 +2354,12 @@
       <c r="F66" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G66" s="4" t="n">
+        <v>485670.7376</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1978,6 +2382,12 @@
       <c r="F67" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G67" s="4" t="n">
+        <v>479895.4935</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1998,6 +2408,12 @@
         <v>478481.1661</v>
       </c>
       <c r="F68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>478481.1661</v>
+      </c>
+      <c r="H68" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2020,6 +2436,12 @@
         <v>475707.078</v>
       </c>
       <c r="F69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>475707.078</v>
+      </c>
+      <c r="H69" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2044,6 +2466,12 @@
       <c r="F70" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G70" s="4" t="n">
+        <v>464907.3106</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2064,6 +2492,12 @@
         <v>456856.3119</v>
       </c>
       <c r="F71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>456856.3119</v>
+      </c>
+      <c r="H71" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2086,6 +2520,12 @@
         <v>450737.5206</v>
       </c>
       <c r="F72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>450737.5206</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2108,6 +2548,12 @@
         <v>406654.2213</v>
       </c>
       <c r="F73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>406654.2213</v>
+      </c>
+      <c r="H73" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2132,6 +2578,12 @@
       <c r="F74" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G74" s="4" t="n">
+        <v>391965.0651</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2154,6 +2606,12 @@
       <c r="F75" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G75" s="4" t="n">
+        <v>373610.2211</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2176,6 +2634,12 @@
       <c r="F76" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G76" s="4" t="n">
+        <v>372035.7101</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2198,6 +2662,12 @@
       <c r="F77" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G77" s="4" t="n">
+        <v>368779.171</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2220,6 +2690,12 @@
       <c r="F78" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G78" s="4" t="n">
+        <v>364313.8869</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2240,6 +2716,12 @@
         <v>349130.2568</v>
       </c>
       <c r="F79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>349130.2568</v>
+      </c>
+      <c r="H79" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2264,6 +2746,12 @@
       <c r="F80" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G80" s="4" t="n">
+        <v>317618.675</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2286,6 +2774,12 @@
       <c r="F81" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G81" s="4" t="n">
+        <v>306593.6026</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2308,6 +2802,12 @@
       <c r="F82" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G82" s="4" t="n">
+        <v>304779.1145</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2328,6 +2828,12 @@
         <v>279571.178</v>
       </c>
       <c r="F83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>279571.178</v>
+      </c>
+      <c r="H83" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2350,6 +2856,12 @@
         <v>276846.4217</v>
       </c>
       <c r="F84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>276846.4217</v>
+      </c>
+      <c r="H84" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2374,6 +2886,12 @@
       <c r="F85" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G85" s="4" t="n">
+        <v>270452.3185</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2396,6 +2914,12 @@
       <c r="F86" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G86" s="4" t="n">
+        <v>265595.8775</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2418,6 +2942,12 @@
       <c r="F87" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G87" s="4" t="n">
+        <v>262311.5799</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2438,6 +2968,12 @@
         <v>253086.7083</v>
       </c>
       <c r="F88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>253086.7083</v>
+      </c>
+      <c r="H88" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2462,6 +2998,12 @@
       <c r="F89" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G89" s="4" t="n">
+        <v>248683.7198</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2484,6 +3026,12 @@
       <c r="F90" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G90" s="4" t="n">
+        <v>245600</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2506,6 +3054,12 @@
       <c r="F91" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G91" s="4" t="n">
+        <v>234392.5508</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2528,6 +3082,12 @@
       <c r="F92" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G92" s="4" t="n">
+        <v>232105.4869</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2550,6 +3110,12 @@
       <c r="F93" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G93" s="4" t="n">
+        <v>232010.2351</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2570,6 +3136,12 @@
         <v>210417.5518</v>
       </c>
       <c r="F94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>210417.5518</v>
+      </c>
+      <c r="H94" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2594,6 +3166,12 @@
       <c r="F95" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G95" s="4" t="n">
+        <v>208196.4767</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2614,6 +3192,12 @@
         <v>200680.3037</v>
       </c>
       <c r="F96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>200680.3037</v>
+      </c>
+      <c r="H96" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2638,6 +3222,12 @@
       <c r="F97" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G97" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2658,6 +3248,12 @@
         <v>193698.4706</v>
       </c>
       <c r="F98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>193698.4706</v>
+      </c>
+      <c r="H98" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2680,6 +3276,12 @@
         <v>189214.5731</v>
       </c>
       <c r="F99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>189214.5731</v>
+      </c>
+      <c r="H99" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2702,6 +3304,12 @@
         <v>184057.6874</v>
       </c>
       <c r="F100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>184057.6874</v>
+      </c>
+      <c r="H100" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2724,6 +3332,12 @@
         <v>179226.4255</v>
       </c>
       <c r="F101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>179226.4255</v>
+      </c>
+      <c r="H101" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2738,7 +3352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2747,6 +3361,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2780,6 +3396,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 16:11</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2800,6 +3426,12 @@
         <v>27004519.2645</v>
       </c>
       <c r="F2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>27004519.2645</v>
+      </c>
+      <c r="H2" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2824,6 +3456,12 @@
       <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="4" t="n">
+        <v>26470000</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2844,6 +3482,12 @@
         <v>23480366.3071</v>
       </c>
       <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>23480366.3071</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2868,6 +3512,12 @@
       <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="4" t="n">
+        <v>23069630.0654</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2890,6 +3540,12 @@
       <c r="F6" s="7" t="n">
         <v>616645.2935</v>
       </c>
+      <c r="G6" s="4" t="n">
+        <v>22596771.7805</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>11672.2089</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2912,6 +3568,12 @@
       <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="4" t="n">
+        <v>20000000.0069</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2932,6 +3594,12 @@
         <v>18754869.6112</v>
       </c>
       <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>18754869.6112</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2956,6 +3624,12 @@
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="4" t="n">
+        <v>17900000</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2978,6 +3652,12 @@
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G10" s="4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2998,6 +3678,12 @@
         <v>15566890.7147</v>
       </c>
       <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>15566890.7147</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3022,6 +3708,12 @@
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="4" t="n">
+        <v>15077130.0016</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3044,6 +3736,12 @@
       <c r="F13" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G13" s="4" t="n">
+        <v>14000000.0458</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3066,6 +3764,12 @@
       <c r="F14" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G14" s="4" t="n">
+        <v>13946038.6243</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3088,6 +3792,12 @@
       <c r="F15" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="4" t="n">
+        <v>13561030.1654</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3110,6 +3820,12 @@
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="4" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3130,6 +3846,12 @@
         <v>12877042.1771</v>
       </c>
       <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>12877042.1771</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3152,6 +3874,12 @@
         <v>12076398.0324</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>12076398.0324</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3176,6 +3904,12 @@
       <c r="F19" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="4" t="n">
+        <v>12035369.0946</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3198,6 +3932,12 @@
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="4" t="n">
+        <v>11000100</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3218,6 +3958,12 @@
         <v>10537438.7702</v>
       </c>
       <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>10537438.7702</v>
+      </c>
+      <c r="H21" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3242,6 +3988,12 @@
       <c r="F22" s="6" t="n">
         <v>-1200500</v>
       </c>
+      <c r="G22" s="4" t="n">
+        <v>9100000</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3262,6 +4014,12 @@
         <v>10145020.9338</v>
       </c>
       <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>10145020.9338</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3284,6 +4042,12 @@
         <v>10064319.802</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>10064319.802</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3306,6 +4070,12 @@
         <v>10050792.1674</v>
       </c>
       <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>10050792.1674</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3330,6 +4100,12 @@
       <c r="F26" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G26" s="4" t="n">
+        <v>9974153.375</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3350,6 +4126,12 @@
         <v>9950177.2448</v>
       </c>
       <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>9950177.2448</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3374,6 +4156,12 @@
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G28" s="4" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3396,6 +4184,12 @@
       <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G29" s="4" t="n">
+        <v>8928368.352</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3418,6 +4212,12 @@
       <c r="F30" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G30" s="4" t="n">
+        <v>8652441.2765</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3438,6 +4238,12 @@
         <v>8363455.9946</v>
       </c>
       <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>8363455.9946</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3462,6 +4268,12 @@
       <c r="F32" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G32" s="4" t="n">
+        <v>8023815.4821</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3482,6 +4294,12 @@
         <v>8023361.3442</v>
       </c>
       <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>8023361.3442</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3504,6 +4322,12 @@
         <v>8000005.5172</v>
       </c>
       <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>8000005.5172</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3528,6 +4352,12 @@
       <c r="F35" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G35" s="4" t="n">
+        <v>7000187</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3550,6 +4380,12 @@
       <c r="F36" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G36" s="4" t="n">
+        <v>6936249.5374</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3572,6 +4408,12 @@
       <c r="F37" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G37" s="4" t="n">
+        <v>6850000.7835</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3594,6 +4436,12 @@
       <c r="F38" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G38" s="4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3616,6 +4464,12 @@
       <c r="F39" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G39" s="4" t="n">
+        <v>6434508.4673</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3638,6 +4492,12 @@
       <c r="F40" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G40" s="4" t="n">
+        <v>6157877.2306</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3658,6 +4518,12 @@
         <v>5674606.3075</v>
       </c>
       <c r="F41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>5674606.3075</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3682,6 +4548,12 @@
       <c r="F42" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G42" s="4" t="n">
+        <v>5565141.3215</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3702,6 +4574,12 @@
         <v>5537959.6635</v>
       </c>
       <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>5537959.6635</v>
+      </c>
+      <c r="H43" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3724,6 +4602,12 @@
         <v>5443778.7854</v>
       </c>
       <c r="F44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>5443778.7854</v>
+      </c>
+      <c r="H44" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3748,6 +4632,12 @@
       <c r="F45" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G45" s="4" t="n">
+        <v>5249101.3481</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3770,6 +4660,12 @@
       <c r="F46" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G46" s="4" t="n">
+        <v>5246809.5221</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3792,6 +4688,12 @@
       <c r="F47" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G47" s="4" t="n">
+        <v>5229000</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3814,6 +4716,12 @@
       <c r="F48" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G48" s="4" t="n">
+        <v>5188888.88</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3836,6 +4744,12 @@
       <c r="F49" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G49" s="4" t="n">
+        <v>5003000</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3856,6 +4770,12 @@
         <v>5000000.0018</v>
       </c>
       <c r="F50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>5000000.0018</v>
+      </c>
+      <c r="H50" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3880,6 +4800,12 @@
       <c r="F51" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G51" s="4" t="n">
+        <v>4664770.6328</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3900,6 +4826,12 @@
         <v>4614481.0346</v>
       </c>
       <c r="F52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>4614481.0346</v>
+      </c>
+      <c r="H52" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3924,6 +4856,12 @@
       <c r="F53" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G53" s="4" t="n">
+        <v>4540406.5588</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3946,6 +4884,12 @@
       <c r="F54" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G54" s="4" t="n">
+        <v>4537210.2091</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3968,6 +4912,12 @@
       <c r="F55" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G55" s="4" t="n">
+        <v>4521268.8043</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3990,6 +4940,12 @@
       <c r="F56" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G56" s="4" t="n">
+        <v>4519500</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4012,6 +4968,12 @@
       <c r="F57" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G57" s="4" t="n">
+        <v>4426640.2635</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4034,6 +4996,12 @@
       <c r="F58" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G58" s="4" t="n">
+        <v>4065312.1229</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4056,6 +5024,12 @@
       <c r="F59" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G59" s="4" t="n">
+        <v>4044917.9442</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4078,6 +5052,12 @@
       <c r="F60" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G60" s="4" t="n">
+        <v>4000014.4373</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4098,6 +5078,12 @@
         <v>3927600.0561</v>
       </c>
       <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>3927600.0561</v>
+      </c>
+      <c r="H61" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4122,6 +5108,12 @@
       <c r="F62" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G62" s="4" t="n">
+        <v>3891798.8644</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4144,6 +5136,12 @@
       <c r="F63" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G63" s="4" t="n">
+        <v>3806790</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4166,6 +5164,12 @@
       <c r="F64" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G64" s="4" t="n">
+        <v>3777387</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4186,6 +5190,12 @@
         <v>3710432.1672</v>
       </c>
       <c r="F65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>3710432.1672</v>
+      </c>
+      <c r="H65" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4210,6 +5220,12 @@
       <c r="F66" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G66" s="4" t="n">
+        <v>3670420</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4232,6 +5248,12 @@
       <c r="F67" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G67" s="4" t="n">
+        <v>3651821.6602</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4254,6 +5276,12 @@
       <c r="F68" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G68" s="4" t="n">
+        <v>3579376.119</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4276,6 +5304,12 @@
       <c r="F69" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G69" s="4" t="n">
+        <v>3534274.8743</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4298,6 +5332,12 @@
       <c r="F70" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G70" s="4" t="n">
+        <v>3500497.764</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4320,6 +5360,12 @@
       <c r="F71" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G71" s="4" t="n">
+        <v>3487322.2855</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4340,6 +5386,12 @@
         <v>3399453.366</v>
       </c>
       <c r="F72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>3399453.366</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4364,6 +5416,12 @@
       <c r="F73" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G73" s="4" t="n">
+        <v>3287999.9796</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4384,6 +5442,12 @@
         <v>3277153.2544</v>
       </c>
       <c r="F74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3277153.2544</v>
+      </c>
+      <c r="H74" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4408,6 +5472,12 @@
       <c r="F75" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G75" s="4" t="n">
+        <v>3217781.3694</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4430,6 +5500,12 @@
       <c r="F76" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G76" s="4" t="n">
+        <v>3203353.2229</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4452,6 +5528,12 @@
       <c r="F77" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G77" s="4" t="n">
+        <v>3148181.9096</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4472,6 +5554,12 @@
         <v>3130293.0222</v>
       </c>
       <c r="F78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>3130293.0222</v>
+      </c>
+      <c r="H78" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4496,6 +5584,12 @@
       <c r="F79" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G79" s="4" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4518,6 +5612,12 @@
       <c r="F80" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G80" s="4" t="n">
+        <v>3032188.4799</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4540,6 +5640,12 @@
       <c r="F81" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G81" s="4" t="n">
+        <v>2856916.0402</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4562,6 +5668,12 @@
       <c r="F82" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G82" s="4" t="n">
+        <v>2728360.891</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4582,6 +5694,12 @@
         <v>2646250.8473</v>
       </c>
       <c r="F83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>2646250.8473</v>
+      </c>
+      <c r="H83" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4604,6 +5722,12 @@
         <v>2603698.568</v>
       </c>
       <c r="F84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>2603698.568</v>
+      </c>
+      <c r="H84" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4628,6 +5752,12 @@
       <c r="F85" s="7" t="n">
         <v>2665.4496</v>
       </c>
+      <c r="G85" s="4" t="n">
+        <v>2585748.6673</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4650,6 +5780,12 @@
       <c r="F86" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G86" s="4" t="n">
+        <v>2578757.6772</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4670,6 +5806,12 @@
         <v>2566060.4818</v>
       </c>
       <c r="F87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>2566060.4818</v>
+      </c>
+      <c r="H87" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4694,6 +5836,12 @@
       <c r="F88" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="G88" s="4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4716,6 +5864,12 @@
       <c r="F89" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G89" s="4" t="n">
+        <v>2489000.3733</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4738,6 +5892,12 @@
       <c r="F90" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G90" s="4" t="n">
+        <v>2470041.0495</v>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4760,6 +5920,12 @@
       <c r="F91" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G91" s="4" t="n">
+        <v>2411374.8288</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4780,6 +5946,12 @@
         <v>2384406.6695</v>
       </c>
       <c r="F92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>2384406.6695</v>
+      </c>
+      <c r="H92" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4804,6 +5976,12 @@
       <c r="F93" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G93" s="4" t="n">
+        <v>2370068.8696</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4826,6 +6004,12 @@
       <c r="F94" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G94" s="4" t="n">
+        <v>2361819.476</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4846,6 +6030,12 @@
         <v>2335954.4783</v>
       </c>
       <c r="F95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>2335954.4783</v>
+      </c>
+      <c r="H95" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4868,6 +6058,12 @@
         <v>2289568.431</v>
       </c>
       <c r="F96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>2289568.431</v>
+      </c>
+      <c r="H96" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4890,6 +6086,12 @@
         <v>2275539.2648</v>
       </c>
       <c r="F97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>2275539.2648</v>
+      </c>
+      <c r="H97" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4914,6 +6116,12 @@
       <c r="F98" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G98" s="4" t="n">
+        <v>2264858.6935</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4936,6 +6144,12 @@
       <c r="F99" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="G99" s="4" t="n">
+        <v>2263684.8207</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4956,6 +6170,12 @@
         <v>2227988.9889</v>
       </c>
       <c r="F100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>2227988.9889</v>
+      </c>
+      <c r="H100" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4978,8 +6198,3298 @@
         <v>2203811.7904</v>
       </c>
       <c r="F101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>2203811.7904</v>
+      </c>
+      <c r="H101" s="6" t="n">
         <v>-0</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Địa chỉ ví</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Token</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 16:11</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>0:05820ee5d06dc31e3ba0cb3eaed05f03b407674df74814e440db790f9a502583</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>30520979.1924</v>
+      </c>
+      <c r="D2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>0:f057f491fc487f0c49f673e331766a05601f68d9e70df6538cd324820a2bbe7f</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>28485323.9097</v>
+      </c>
+      <c r="D3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>0:a2db3dc9758c09da38c9744911fa4767bad013a222e60edf18e902f41d3fa7e4</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>0:6840bb9aab31c28a45695981834acf855508b3feb0f1898a016ef3935b372eeb</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>14808642.0248</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>0:a8f641e2c97deabe8bef338d20387f07fa4ef71e2b0c7d27f9c6ae4c15378fd7</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>13955655.1909</v>
+      </c>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>0:779dcc815138d9500e449c5291e7f12738c23d575b5310000f6a253bd607384e</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>13650572.8907</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>0:d937ea6475fef35f05175a75c182cc582a3a04441fbb0110848d2df97ac3b03f</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>13363396.9665</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>0:389328b9cbc1fb3f28e2b335609a5fad65bd62d3d5a5edb870accc47837be316</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>13055036.4516</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>0:01eb869f58cc270a97cd8be9ab21558580cd71fa9e384e4700f4dfaddf759c38</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>11877969.9425</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>0:db35c6aa8a7bd0cbfe039de5af3cc95614f8a4adb341fa731620c2fed809a507</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>10950000.9992</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>0:d6ed14afb32e9efb7c58d24839c025eb87d7e1aa17ddaba3529c72bc20249917</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>10497910.9711</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>0:374dcef51d52dda07444379c52965375f5f723a2cb41430c85822e843f446587</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10466354.1133</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>0:0000000000000000000000000000000000000000000000000000000000000000</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>10000352.735</v>
+      </c>
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>0:a201927ad1fc0783b98d30c12f534b9fd2a044096aaacbb0482d4c85457646b5</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>9703974.7772</v>
+      </c>
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>0:ac1e0e46d16129acf447ced89eebe60236b3d05729024370501defc744b0974b</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>9081000.1829</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>0:2fcbc568f85fffe6e89ac871434b2b22568e802743fa84fd184ac46454436e95</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>9045888.3857</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>0:b7c0961aaa0f153431b3b0624f48082b85c4c4117d24106e4718858732e050f5</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>8722578.914100001</v>
+      </c>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>0:f38b95e5366811c8c1b217ab4748c6388c8ca357ab218baf32fa813f306afeee</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>8711385</v>
+      </c>
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>0:04fc14406f27780f147343227ddb37fbb8632ff620eee9a87dee02492e3b54b0</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>8651347.4691</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>0:6af9af4b65bfce0605bd815fcc4697ffd6443f539f9a1e84174c642c4517a783</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>8401023.438300001</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>0:8a985fb077fb7d4fe9000d12962ae177ee8cffba14f0f6239f678f2e9b6b6856</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>7904138.1249</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>0:b454b08b0c082e5ea54df470aef742d6cc9fb63199451c0520638b74194048a7</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>7753623.1938</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>0:ae4ec8024f912a85e53336a4d4dd68ee104201a977f7a6391deccc0f3f470b4d</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>7445008.5622</v>
+      </c>
+      <c r="D24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>0:c89d8d2ede6a29fb990c3cde29a344a337664a70abb61a39fe7a8f07d368d562</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>7229423.4285</v>
+      </c>
+      <c r="D25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>0:60e953ed1b7d249e45a5f87fa39295437bbecdd7585b48d1a817c6df83350dac</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>7124816.6694</v>
+      </c>
+      <c r="D26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>0:0b139b38d648c4b63d88730ff4a65d1f6dfadcd899f8ee3361640ce189893315</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>6904270.1775</v>
+      </c>
+      <c r="D27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>0:c654682d8c4797b87681af9f275337e8039808e89d9ce0496614b19205405620</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>6847950.1462</v>
+      </c>
+      <c r="D28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>0:4e0a2b8adecb6dfa785538f0baaf4196159634d64dce0218db0a8e4d84fd0d5f</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>6836034.0034</v>
+      </c>
+      <c r="D29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>0:fef7b00ea7006211d4f4a281a2e78dcf65bdb9c5bba93a54947af42246d5c9c6</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>6574441.9423</v>
+      </c>
+      <c r="D30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>0:ba828a54ab47665da11c83987724c308c8d67d2c8186d72cc2ee9c5fc6578f9e</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="D31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>0:cdd3233d21f8bf90726e710c80279a9413d3558fcde04c32f0f475dffa9b523e</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>6148640.0548</v>
+      </c>
+      <c r="D32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>0:1d9b08328908e982b0f05a6bfc03e0fab8ee8c7056c93f7d31e1a0b554965aa0</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>6116138.8294</v>
+      </c>
+      <c r="D33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>0:0c1406184e80d810e5beaa394653b1844295af3f6b196438d81304884675ae4a</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>5989650.4407</v>
+      </c>
+      <c r="D34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>0:4b9f356664fa3f9981a1cbe786d8933223184ba30c40d10fc43594458220f54c</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>5913624.5861</v>
+      </c>
+      <c r="D35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>0:bba481f73d8bee9093c147bbfaf4bd0ce09e4931b7a4c7c93e54dbd33a2ba243</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>5745360.968</v>
+      </c>
+      <c r="D36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>0:49da119bcdc22c15b72d95a184529997b656da65b736c903cb2131e750fa3dc7</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>5560234.6103</v>
+      </c>
+      <c r="D37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>0:678dafe483da659bb1ca3215a249742bb5c58c13127a422dbceb572317ffe200</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>5213528.6062</v>
+      </c>
+      <c r="D38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>0:7b5dae27d6725e1c0175ebc26cb0c7393638e2c68bf567516de0c5c8fb14ff54</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>4734322.9228</v>
+      </c>
+      <c r="D39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>0:d98d77eea8bd232bfbfb928383ad12705e74309d18e4d61464a598ee4cb82e2e</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>4683092.749</v>
+      </c>
+      <c r="D40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>0:7dbbca2ecad6fe883a97db9e7b07df9ebc838161d24e0be5dd509d9ba0dcc816</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>4611862.884</v>
+      </c>
+      <c r="D41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>0:bc250333a680f6d1569c89588a487abaa757dbfd460d7ece9806df7cac911d03</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>4393891.0983</v>
+      </c>
+      <c r="D42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>0:bccc2f25164a2e779e354f00d6192385d73402047d2de5e2f3706085ce13035a</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>4368320.2419</v>
+      </c>
+      <c r="D43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>0:590c784c7459c328991d8acd3e5f8537542086f24cc70f2426badd419c8044a4</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>4283944.4597</v>
+      </c>
+      <c r="D44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>0:d9732f35e58caab943e35e069bcba417da8565c69b39f0a4d68d97cf521a8399</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>4283680.8613</v>
+      </c>
+      <c r="D45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>0:9328fc4c5677ac329358d4d6db2a7d02ced1097b581a11d56e18e4d1c898b3bf</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>4263304.9862</v>
+      </c>
+      <c r="D46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>0:13bf4f871733b2d5ce5df128a472f32b1fc83cb80c5d0649210d62ce2a622173</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>4232810.3687</v>
+      </c>
+      <c r="D47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>0:f7581686f7619adfc3969565123995d93a3b19b655b02bbfd746e5c95b916cf2</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>4155860.0882</v>
+      </c>
+      <c r="D48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>0:41ac6bbbae604d2b2cd8b8f2b85a29a17e5f8a6c8ec16fcc909b44ba110cfb99</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>4129406.5164</v>
+      </c>
+      <c r="D49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>0:270c89da8160a9c62d42dcc59b91c132af8334c728cc455d3e25eda8fd56e723</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>4125367</v>
+      </c>
+      <c r="D50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>0:23f15cd27bd73c1f9a31a3d86f42a5edee6346f50cc6a21e04c9831f182c5382</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>4001000.0311</v>
+      </c>
+      <c r="D51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>0:0fad4569f2eda170fdecbb479c2a8738d65461f0f4c8f914d9e37b457ecd4c68</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>0:2ff803e3d5df27c30e57318b5a1dd407cf709bfc6aaa62216e89fc2efcd6c18a</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>3905978.0445</v>
+      </c>
+      <c r="D53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>0:be42f52d5fc711ba8813f323d73825256083e7f2ac4b72e274096e0ef63656b6</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>3900000.6952</v>
+      </c>
+      <c r="D54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>0:6f25807af5789ce48a9cc539c90ed9dfb03a9cde9178916613598ef0f0013678</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>3660840.1514</v>
+      </c>
+      <c r="D55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>0:d57a3fc08e41f2e7051967e9a7cd57bb44642758e6bc8ec3e0dbe6f6a7c89072</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>3600815.2143</v>
+      </c>
+      <c r="D56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>0:8d9cbb1b2e55fc04c8cb85f9e4fe0aab82d9fdce56a332f9cff54c37c2347aca</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>3521971.5871</v>
+      </c>
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>0:a6413beb2a98e05762d44f13564723a5622014a57d56ac8fe6eb08b78691379b</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>3500100</v>
+      </c>
+      <c r="D58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>0:3fe8417a2106d996681201db94e83ef718c73587e8154ba242498830d8d3ac54</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>3483829.0767</v>
+      </c>
+      <c r="D59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>0:ce845fb24e6392467b5e24eba67cef01456e459722a18a4121ae53e12b9ec363</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>3394243.2595</v>
+      </c>
+      <c r="D60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>0:f2d218624dbd83c492074adcc643d879a97295b65b97abd94fc6d63786728c1e</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>3383497.4498</v>
+      </c>
+      <c r="D61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>0:796df20230c57433a65ec1c8d9dc3c116ee01291e4c49f0ed1abe0bf2ea91f7f</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>3368404.471</v>
+      </c>
+      <c r="D62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>0:94e3b17a4918492d81cde639fc7ca3214d457f679118d108fbd7dfbb91e1f6ad</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>3245658.8196</v>
+      </c>
+      <c r="D63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>0:5e89652580caa0719d8c2f34d70346aa868c91421cd2811a3cf32b0e53cba5a0</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>3140000</v>
+      </c>
+      <c r="D64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>0:e048ea358169358c0f0b71ac0b7f37f14f4b900e67413bb6308701d3b03ef270</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>3137170.579</v>
+      </c>
+      <c r="D65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>0:b349a98792a1b3298702ed6504baafe86e19e447ddd41a4c18e2b0cf31e01b37</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>3123654</v>
+      </c>
+      <c r="D66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>0:37713a0d93df7bcd749eaa7006b5caa187b840268bf7d1a65b61c3aeb58acae0</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>3091319.0383</v>
+      </c>
+      <c r="D67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>0:2a48009abf0011b6206a430b8dcf8d2f1d533e3c1394091f5b59382ff7f1b856</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>3072698.763</v>
+      </c>
+      <c r="D68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>0:450a9aa768bccefb443dbac7a30703da1dd9bbf30089aae1949728cc5453ae70</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>0:22d47706f14dd20c04b4153d1419e128baf48182901733cff5ecad4575040a8c</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>0:1f158e38cd8251289f1278021a5613d569c497cd9d0db0d4493a56fcaf5da298</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>2973872.3136</v>
+      </c>
+      <c r="D71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>0:441db70005bbfd1d942c7e36c2324e2a3a2a6abf53cdcaaa612973ae4acdf66d</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>2950633.646</v>
+      </c>
+      <c r="D72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>0:bbfeeb1e32cb5a8e9f48c395170c46641cbca11cbefe393a4ff15d81bdfc345c</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>2909500.9876</v>
+      </c>
+      <c r="D73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>0:921eac964c0968f9a344613a48b89033cc449b860054eb62b60f525640c40e02</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>2891843.2925</v>
+      </c>
+      <c r="D74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>0:66cec988ed6a39553375bc16c77945bb91f5a869ab0675a6d9aa41dba805f19a</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>2881207.2314</v>
+      </c>
+      <c r="D75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>0:b74473e29bf4e2dc5858909e9a11381d4ae58d2cab91aa02f84d77591d5d311c</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>2840623.0813</v>
+      </c>
+      <c r="D76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>0:f8f492b2c363e949632591cfb10430fb981a38ea577821b4e3bdfcead705b404</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>2807640.3471</v>
+      </c>
+      <c r="D77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>0:1f632e4aa77e148db32499329a3c35333bb338c8453d9226cfb96fdd9b55edd3</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>2788208.7317</v>
+      </c>
+      <c r="D78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>0:896c402745117b7e6c3318a65fa6437a30ffd0dda1ef3d7285837474a04b2697</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>2745744</v>
+      </c>
+      <c r="D79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>0:140ddc3d2fb26c3c3daf254d73f18a0b0cecc8afa68ff7a3fa6c22f52a19d983</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>2700000.1965</v>
+      </c>
+      <c r="D80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>0:f70de80d86241c3a84059e9571469232f7324421c00ce70b040f17cbb8b23f3a</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>2606056.9299</v>
+      </c>
+      <c r="D81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>0:a94f15a1632a32bb23063a23a88a113b485258168b72219b9f07220433827e4b</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>2581406.1876</v>
+      </c>
+      <c r="D82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>0:da303a41fd89374b3318bde79a42ef3789a98dfd24de1b7ac54140707e1c7027</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>2574029.367</v>
+      </c>
+      <c r="D83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>0:99a291430a326719583b1855a5d39466adaf44953172d9334d3980ec9eda5e5d</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>2558018.4975</v>
+      </c>
+      <c r="D84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>0:35191a9f4ab3740d853f2accb2cc91644096b36f61a2b6c33f743f3052eb0ff5</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>2514361.2647</v>
+      </c>
+      <c r="D85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>0:01f22c3e72ebc265eb302e42ab316d631297b14bc76a2e3183c1e95e2a34825c</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>2433024</v>
+      </c>
+      <c r="D86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>0:ca149ef825ab73b6575f5755625dfad8fdcf594c52ddf9c764ac42b346c39f77</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>2419271.9384</v>
+      </c>
+      <c r="D87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>0:049b7cffc8296331887501e280f5a39d125fed063bd08cc4c3dda7d5dbc67223</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>2403417.0469</v>
+      </c>
+      <c r="D88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>0:ac985ecb77476b3fb4cae6ee15b1d13ef8dfc906a1575a66ce7c3596b4e91b1a</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>2390187.2657</v>
+      </c>
+      <c r="D89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>0:e542dafcefa76eed90cd44d6201b558f9cfed48e10073af3d2d5eff7764c75fb</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>2355571.632</v>
+      </c>
+      <c r="D90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>0:8f6985cb83fcd1ce561ea858c16c7ab2a44609c5eaef37f67027bc6141d5164d</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>2344726.8593</v>
+      </c>
+      <c r="D91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>0:c5f4e6829ceec79350cae0988656f7a4bccaf53058d629b3364bc9e80a8be4db</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>2300000.5926</v>
+      </c>
+      <c r="D92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>0:ac9b47205d4e9550f462d9f69904160bc7ab5b70621043b172f2f9b37ba89831</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>2278552.7571</v>
+      </c>
+      <c r="D93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>0:d46026467f69efec5baebeb4eaaa38b3024523f05902be99a70d5357bca1404e</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>2274832.8859</v>
+      </c>
+      <c r="D94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>0:ee62d77d8f2451b3815062721194ecf3b99d3c7005c642941a681a77be8c858b</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>2268074.3017</v>
+      </c>
+      <c r="D95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>0:65ba6d5e763d5fc30450228213666e0e1e7a1805037bb2f5e62cfa23fb8cfaf2</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>2223000</v>
+      </c>
+      <c r="D96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>0:57ea169cbd0270e40fab6ec75b3074d401a579e13014cb2bafd5c20dc02e5fdc</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>2214975.5538</v>
+      </c>
+      <c r="D97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>0:cf563aac43f868c50503119f2d496fd4152977301f50722494b737325f57f72d</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>2181764.0737</v>
+      </c>
+      <c r="D98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>0:c0bd296c37f04cea8e89dada87632f6ff056819d3d0603fea99819639acd3f20</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>2169709.2706</v>
+      </c>
+      <c r="D99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>0:cf319be786f6e19d4be7734bd7175935ac898457bc6fe750f4518ef0c1347d12</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>2071580.1255</v>
+      </c>
+      <c r="D100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>0:052f8fb1c09be11802e535f7ae063bd73fd7b470a5a9e528f8471f4a6703009f</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>UTYA</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>2038371.3021</v>
+      </c>
+      <c r="D101" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Địa chỉ ví</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Token</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>05/08/2026 16:11</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>0:d887d0e2d1c4fc4126e71c970d33ab1896940000eae703bb1ab6cecc830777e3</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>4976700.4092</v>
+      </c>
+      <c r="D2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>0:779dcc815138d9500e449c5291e7f12738c23d575b5310000f6a253bd607384e</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2313347.1807</v>
+      </c>
+      <c r="D3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>0:a8f641e2c97deabe8bef338d20387f07fa4ef71e2b0c7d27f9c6ae4c15378fd7</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2214286.191</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>0:1b84c5a8b28c5ea174c98bd4e5c34f4c1233d5bdd25ef63d270ba2baae8d1dd6</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>2106038.2213</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>0:d629d8d740c17af8fc2f244e2a34abb6680cb5b69a9f6143f3b092f3c622d260</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1172275.1874</v>
+      </c>
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>0:086fbb7a031d407757317c9f0b277600b16142393f600e20cbd4379c83cf9252</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1053611.1676</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>0:1295b3d44460506ab0dc1568d7b14a7ce97b4d5e747abd822dc9f2e3bf98a702</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1046924.3234</v>
+      </c>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>0:34773f1472a48f08af65619351de183c11c6707b241c8fed05b8f6a10f82266e</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1019712.413</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>0:7b0dcf0a1c4446ea0894cfa5a4c929e4630729d6e106a220ad056c4b25aebe10</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>0:153068d0ba386b012128fa7d883219ec9edf500172a2d9c7f41f04719a0488b8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>897950.7675</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>0:ee2e0f3bb688dcefbb22952f14e1111bbd1674b496dd936c841d3d5557f7c8d8</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>823887.4096</v>
+      </c>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>0:e6931fea1e4ffa661f9add3fbf46bc2de281d7d624e1b8e42e1917a5abc60b41</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>777000.2937</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>0:450a9aa768bccefb443dbac7a30703da1dd9bbf30089aae1949728cc5453ae70</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>750000.001</v>
+      </c>
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>0:c5f5cad02fc7e7b6c0a5bfddeeb52ba403449553d5eabbd831db3b35998a6c40</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>750000.001</v>
+      </c>
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>0:0b139b38d648c4b63d88730ff4a65d1f6dfadcd899f8ee3361640ce189893315</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>700000.231</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>0:1b39d40b6ba09ed5f1329bbc0ceb06f7406516f78914a96c8df7738115ba17f8</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>686827.8777</v>
+      </c>
+      <c r="D17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>0:bd0b99ade222b95c51b77b9e95f36d3bdbbd657c23dafe67452866c8b1403d5e</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>627640.3759</v>
+      </c>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>0:959284cb0b56e0a244d06a0c85222377fdd3881d771ee6b8ca2c4fbf127f117a</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>599513.0695</v>
+      </c>
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>0:58ac8dc106746514aeb4aa49c0b0c4041f38464ca4bf3f8a6e9e6279a3e7f73a</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>588698.001</v>
+      </c>
+      <c r="D20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>0:1a536bdec3f7b799e390af78865b77c63918a5f44a65e7a37aa718d5ed03bb30</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>570000.4782</v>
+      </c>
+      <c r="D21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>0:92df38eaed7d0793f8eb59e96fd8612ae1a88a747661a89d79aab8ae1f73676d</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>545239.751</v>
+      </c>
+      <c r="D22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>0:1ea4e7c10440f983b86d4f49a9cbf512875a2ec6c4e5cdf9d8bf3ef847a60f78</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>539889.8815</v>
+      </c>
+      <c r="D23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>0:f2d218624dbd83c492074adcc643d879a97295b65b97abd94fc6d63786728c1e</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>523466.0617</v>
+      </c>
+      <c r="D24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>0:59bda7dc5de3f373d1e4717870c5f6a331d50b27a28c8b3e1256a2766ebdc38b</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>521487.3899</v>
+      </c>
+      <c r="D25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>0:ced05b0bae574e4e61839ff38a3f1e76b017d97fffa2a556a242129b8c3ac152</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>501931.2321</v>
+      </c>
+      <c r="D26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>0:6840bb9aab31c28a45695981834acf855508b3feb0f1898a016ef3935b372eeb</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>498061.7132</v>
+      </c>
+      <c r="D27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>0:00124bf6011acf05cbe437c33594b35ae38552993a7d723805ba0b72cd4739b7</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>470548.7919</v>
+      </c>
+      <c r="D28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>0:b9fa0ddf3a9ff62c904f7835f7463fe35b5dd614b42d8b2f91a6648c85ee6f0b</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>450108.8158</v>
+      </c>
+      <c r="D29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>0:a14b1f452385b2bb984ad2c4441e1d23cae071fdfc096dfba53ebba3b6ff1d10</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>415714.3805</v>
+      </c>
+      <c r="D30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>0:2fcbc568f85fffe6e89ac871434b2b22568e802743fa84fd184ac46454436e95</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>408223.1085</v>
+      </c>
+      <c r="D31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>0:f485346e9dd90eec57c392953b42a0ad0d3239157ba124ce69d4dad2383cbd93</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>400238.9755</v>
+      </c>
+      <c r="D32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>0:72398ba2fc178af142340c0cddd14bda48eca0d038b4f97d19b0adec58c87940</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>370000.8927</v>
+      </c>
+      <c r="D33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>0:032688e2f6f239a9f0faad32e384c77d34811277a49fab65085a1f271dd90e2e</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>356213.8346</v>
+      </c>
+      <c r="D34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>0:18cb9d696ab459ce3a0ec24b394441e7f2c94ecd68bd344e56f90390560bd3bc</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>348972.7294</v>
+      </c>
+      <c r="D35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>0:623f58810b90ad5575ee25d78b92fdf03528eaeca92e3155b9fe0c43c62b685e</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>344999.7763</v>
+      </c>
+      <c r="D36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>0:790ebf38ac74ed3ac1d9630068444234713e4a2e68623b6ff352718cc997fb20</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>343179.1316</v>
+      </c>
+      <c r="D37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>0:c3e69fdca0965430cea0fb84bf39159fc8f9925aa3f1bbdc7944bf5bd2ce0aa4</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>326484.5328</v>
+      </c>
+      <c r="D38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>0:6dcb803c9af913c599564ec23ab277040857b82875bdf486851053a835cf176e</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>326060.7935</v>
+      </c>
+      <c r="D39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>0:46058382332a885b40702c383096822adab86ad217e0cf051cbd65dcff278137</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>306577.9649</v>
+      </c>
+      <c r="D40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>0:c0bd296c37f04cea8e89dada87632f6ff056819d3d0603fea99819639acd3f20</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>295536.9332</v>
+      </c>
+      <c r="D41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>0:d4a3a50a7fbd117d302ad3cd23c2947f5b552bf8b8e4bd4f89b2329d131972e0</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>293786.1018</v>
+      </c>
+      <c r="D42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>0:866281e6fe85a90cb428b6348861e319cd619ac068772d9af87494b58fb146ac</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>285000.001</v>
+      </c>
+      <c r="D43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>0:a2faca7adfebd5c5970108d1f79065cef32b0c143fb13489066b684cdd7ee95c</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>281629.4939</v>
+      </c>
+      <c r="D44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>0:fe67a0dca2b2135aacc3874ddbaff48c6bef1517e584b6cd323c02017b9c9074</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>271817.0389</v>
+      </c>
+      <c r="D45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>0:745331ff27449097d77ac732b84f70190f7ec9d59eee5d12801466e12f9945e6</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>267461.4365</v>
+      </c>
+      <c r="D46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>0:6d767be8253fd042af7048d04a93db2b560a3ce3a0032644a98547e9e894f096</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>264414.4323</v>
+      </c>
+      <c r="D47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>0:17db115142cfd4042c3506426a0d8e2e1d4cb4ffae703a4f8839b24d5ec99861</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>253677.9782</v>
+      </c>
+      <c r="D48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>0:bf84e988ad26f851116b931102cf6fcdf1fe2afe1d7390c241e2a93955d09846</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>251513.5263</v>
+      </c>
+      <c r="D49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>0:b026f35996f084d2c0f8c545dbde93e433d8e03d1bc5023e737581dcd3964f00</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>243482.9412</v>
+      </c>
+      <c r="D50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>0:eebc80fa9be53c4a5f5b91b7a3798f7847b9697473e1bbec7c5228b91f8b54b6</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>241310.5368</v>
+      </c>
+      <c r="D51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>0:6b8bed017e8b74ba087747ad956d92023e24de66d4c71a731d20c346dea416a7</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>240561.9116</v>
+      </c>
+      <c r="D52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>0:1dcf52bc6282798811489a6eb589995c9ef9a9442a7d3a0b89263beccf256e0e</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>236974.746</v>
+      </c>
+      <c r="D53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>0:f27f92aac9613a65c0f0427c174b592d13593ba368bace5bfcd0bf0f52d5bbc5</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>233629.5261</v>
+      </c>
+      <c r="D54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>0:bfa32176551ecbb94d3f0a57f32760b9b278f423739f06bea34272288cd1d89b</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>231622.8616</v>
+      </c>
+      <c r="D55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>0:cd1cf0b39fd76b1f47c6247f7f59f77d214e3bffb9635bc598ed4ccc4e562f4f</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>222266.5693</v>
+      </c>
+      <c r="D56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>0:339c6a24938f3f09abc7025554abb6ca7ec7dc8e7f54197439b054f220a23d29</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>217465.3479</v>
+      </c>
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>0:276dab506f4fb26a77045a421cc70371c37ea987aa41bbf08e92406035167a73</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>216566.8413</v>
+      </c>
+      <c r="D58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>0:ca74478546cb70edae5fea13cf684375dad7ca8c34b67bc36eb2e5f8c7806889</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>212280.9443</v>
+      </c>
+      <c r="D59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>0:a08d64a1cad9ecbd8a7ce66a3c784f5cbc6ea868634b2e6a58c609305828c332</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>211426.2168</v>
+      </c>
+      <c r="D60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>0:c7ae3a0653af5f7cf0c27fed5278e52bb72b02827f39daceb1c808aaf68d19a2</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>206815.5368</v>
+      </c>
+      <c r="D61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>0:d166788b27bafa856d44e2bc78a29089bc36c9251b2dfb72d435bbc19d0cb63c</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>202410.95</v>
+      </c>
+      <c r="D62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>0:ab7e7994490537d40430cfa36f940f480d4e6dbaa5771a3e88f6b680d238eb88</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>200460.2851</v>
+      </c>
+      <c r="D63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>0:b496b8f73b469ff06a2d89e62c4d70a103fc228c821537b49dff092060bc281f</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>200366.4286</v>
+      </c>
+      <c r="D64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>0:6427d012ad3dc33b58c4e2b375a2a37570d7aa618037c5f97eaa93f52e566978</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>200100.0027</v>
+      </c>
+      <c r="D65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>0:2d148675777be5513730276a184b6f23d9578e6f6263c6ef8be1704427fa16c9</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>200000.003</v>
+      </c>
+      <c r="D66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>0:e542dafcefa76eed90cd44d6201b558f9cfed48e10073af3d2d5eff7764c75fb</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>199229.0666</v>
+      </c>
+      <c r="D67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>0:c2d11c507681255a42a5f1b56c6de2c5c209c209435823b4ef473d1361c7cbd5</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>193403.8264</v>
+      </c>
+      <c r="D68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>0:42a968a62c365dd0724ca47f7d9d6397cd7a04c675f480ab634e2e69ed8802b5</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>190133.681</v>
+      </c>
+      <c r="D69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>0:8b4c7efa0846ec28f0cdf367d517a7693fc9e56ee8907f60be7f41cb46a215e0</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>185707.0997</v>
+      </c>
+      <c r="D70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>0:211ebad791001672693afc9c2093889846f1a2d3b6f6886c3078caf9e7a31e37</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>169133.0666</v>
+      </c>
+      <c r="D71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>0:9d3499984ea20878075032da661efc8cf9a06e25004744cd06c8edb5feb08156</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>166366.5773</v>
+      </c>
+      <c r="D72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>0:8c4fbc03b8d41283cca1d60b3475387ea606f14e86b0f67aa0772d338eb870c9</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>162771.4522</v>
+      </c>
+      <c r="D73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>0:7fef28f86bdf4ecd0f911b560aab614f8d9f3186c3cc759835303dacbb53f14f</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>158819.0758</v>
+      </c>
+      <c r="D74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>0:af594d82d939c18ae04d3b5fe722b29c4d0e2cf563cd0726ce5a6ae905fdf4fd</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>158686.0651</v>
+      </c>
+      <c r="D75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>0:677781bc17fc925fef347b2a8a02afd7f5a5bd0708aca04498e68208cae9f347</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>156656.8749</v>
+      </c>
+      <c r="D76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>0:7c443dd6359b1e419f8d9e9eca69ff7ccd63c9365fdc47167306cddc36a40cc7</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>155914.8696</v>
+      </c>
+      <c r="D77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>0:f964f3197923139252be9004e0b8afe12cd4edb2d1cb4cef4065b411a9d741c3</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>154759.2409</v>
+      </c>
+      <c r="D78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>0:cb77ee35b71a853103e9c787fe58fe6c65a641dcf16bea9dcc6ad7408fff2016</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>153035.4628</v>
+      </c>
+      <c r="D79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>0:4a07f1a5b148794a71c184425dccc3c7f05eb3339595d15d1bf6908fbe4434e2</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>151610.9121</v>
+      </c>
+      <c r="D80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>0:77bb6079c247e55749f91ea7f9907235c04ec90816fd954ee66724d6a5fa120f</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>151424.8522</v>
+      </c>
+      <c r="D81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>0:b980e0723bfb26ca953d92d9e3d696002562339bcf1abb54808c93dc19b30a71</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>150487.8467</v>
+      </c>
+      <c r="D82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>0:450c0691a465922a1dc9ba41b10f1f16f1766f9d5724907c5874715c0abdda5c</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>150302.4017</v>
+      </c>
+      <c r="D83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>0:d9afb7e4bacbb3a4d68100f0b5ab973c96911228a827803fe733ec4dad5e7adb</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>150036.9878</v>
+      </c>
+      <c r="D84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>0:1f91b47208e19df21c30e49db7dc74c6febc2a23cb3eca91e02facbefe62b3a4</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>150000.6498</v>
+      </c>
+      <c r="D85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>0:32a73076267099f4ee1fa998c85ee71322c72523087cb00ca4198a34e7af916f</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>150000.001</v>
+      </c>
+      <c r="D86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>0:038fa7b8e31537122c9d9ba55e08c8084ec6fb2c9c93c298e72f95170de13b52</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>149900.0082</v>
+      </c>
+      <c r="D87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>0:35c9413a645c3c575680881c3bd93969a8eae1a7be15511000035266d0c622eb</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>147428.1548</v>
+      </c>
+      <c r="D88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>0:a11e2700f39d416e56217840cdb17add47af8bcdbac5357580282d451a09318e</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>146885.6077</v>
+      </c>
+      <c r="D89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>0:45eaca696d65eb40e2f0a26ab73c8a060dc20ea94db8855d3a7e04cff05945fe</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>146758.535</v>
+      </c>
+      <c r="D90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>0:18d6ccb5e1fe52a8369446f37013e939a655a1c82a7d03f1a9c1cedf0b06a920</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>146641.7138</v>
+      </c>
+      <c r="D91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>0:064bb34e8f7f22966b8f4b206f45e91a270fec787e9cfa1716778a572e9c497e</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>146516.2953</v>
+      </c>
+      <c r="D92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>0:5d5535f27b6251f893064e79c25bf5f39bc8ef697af17be46ab6091bfebddb1a</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>146113.5092</v>
+      </c>
+      <c r="D93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>0:934a4d510790b95b380261babe0a880a10dc8f2890fcfe5a6d6b77c040e5ca7c</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>145794.0494</v>
+      </c>
+      <c r="D94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>0:d5b08d092679c72f66ee943b18571da268be437c088030f7b37ad6fc4a6148fc</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>145000.001</v>
+      </c>
+      <c r="D95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>0:0bf2eb3935f43c119874df813c8adf7e0234d3ff972c7aea79742ed87d69dbfb</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>142277.791</v>
+      </c>
+      <c r="D96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>0:ba5ff233bd79105aea2b280dfe6d45eef8bbd15a5949ad1afd5cfec293a071bd</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>137164.0534</v>
+      </c>
+      <c r="D97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>0:db35c6aa8a7bd0cbfe039de5af3cc95614f8a4adb341fa731620c2fed809a507</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>137000.6095</v>
+      </c>
+      <c r="D98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>0:ff06d10b475ad90245e14490cdcb5f6cf05b9b869c0dadd01dc0a3090f5a85d2</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>136857.5203</v>
+      </c>
+      <c r="D99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>0:4a262d2f78acdd2ff6a51c4251ffc25db87b74378a77e09e2edd5532a88e1690</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>134975.955</v>
+      </c>
+      <c r="D100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>0:bb323cdf01512f0b4a4d707cf556b90b4f46b894f72adce3ea1b6da8d1ffecc9</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>132924.65</v>
+      </c>
+      <c r="D101" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/theo_doi_vi.xlsx
+++ b/data/theo_doi_vi.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -497,6 +497,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,6 +542,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>06/08/2026 08:01</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -568,6 +580,12 @@
       <c r="H2" s="6" t="n">
         <v>-42772.8434</v>
       </c>
+      <c r="I2" s="4" t="n">
+        <v>6175237.377</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>-20536.4888</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -596,6 +614,12 @@
       <c r="H3" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I3" s="4" t="n">
+        <v>4593414.2832</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -624,6 +648,12 @@
       <c r="H4" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I4" s="4" t="n">
+        <v>4032682.9341</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -652,6 +682,12 @@
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -678,6 +714,12 @@
         <v>3663634.4136</v>
       </c>
       <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3663634.4136</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -706,6 +748,12 @@
         <v>3628524.82</v>
       </c>
       <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>3628524.82</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -734,6 +782,12 @@
         <v>2743926.9899</v>
       </c>
       <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>2743926.9899</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -762,6 +816,12 @@
         <v>2407572.5386</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>2407572.5386</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -790,6 +850,12 @@
         <v>2000000.0012</v>
       </c>
       <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>2000000.0012</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -820,6 +886,12 @@
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I11" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -848,6 +920,12 @@
       <c r="H12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>1938773.4789</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -876,6 +954,12 @@
       <c r="H13" s="7" t="n">
         <v>30029.8717</v>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>1998235.5688</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>157291.4669</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -902,6 +986,12 @@
         <v>1663791.3571</v>
       </c>
       <c r="H14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1663791.3571</v>
+      </c>
+      <c r="J14" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -932,6 +1022,12 @@
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I15" s="4" t="n">
+        <v>1377367.2208</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-123947.6705</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -960,6 +1056,12 @@
       <c r="H16" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>1236777.8944</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -988,6 +1090,12 @@
       <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I17" s="4" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1014,6 +1122,12 @@
         <v>1178546.0449</v>
       </c>
       <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1178546.0449</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1044,6 +1158,12 @@
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>1173068.8403</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1072,6 +1192,12 @@
       <c r="H20" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>1075254.7301</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1100,6 +1226,12 @@
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I21" s="4" t="n">
+        <v>1070173.9749</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1128,6 +1260,12 @@
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1154,6 +1292,12 @@
         <v>1027286.3894</v>
       </c>
       <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1027286.3894</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1182,6 +1326,12 @@
         <v>1023082.1439</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1023082.1439</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1212,6 +1362,12 @@
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I25" s="4" t="n">
+        <v>1012395.8946</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1238,6 +1394,12 @@
         <v>1009987.2763</v>
       </c>
       <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1009987.2763</v>
+      </c>
+      <c r="J26" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1266,6 +1428,12 @@
         <v>1006825.8922</v>
       </c>
       <c r="H27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1006825.8922</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1296,6 +1464,12 @@
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I28" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1324,6 +1498,12 @@
       <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I29" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1350,6 +1530,12 @@
         <v>998014.552</v>
       </c>
       <c r="H30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>998014.552</v>
+      </c>
+      <c r="J30" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1380,6 +1566,12 @@
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I31" s="4" t="n">
+        <v>990000</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1408,6 +1600,12 @@
       <c r="H32" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I32" s="4" t="n">
+        <v>979187.2334</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1434,6 +1632,12 @@
         <v>889548.5399</v>
       </c>
       <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>889548.5399</v>
+      </c>
+      <c r="J33" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1464,6 +1668,12 @@
       <c r="H34" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I34" s="4" t="n">
+        <v>887524.782</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1492,6 +1702,12 @@
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I35" s="4" t="n">
+        <v>879501.0418</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1518,6 +1734,12 @@
         <v>862367.0839</v>
       </c>
       <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>862367.0839</v>
+      </c>
+      <c r="J36" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1546,6 +1768,12 @@
         <v>838549.1449</v>
       </c>
       <c r="H37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>838549.1449</v>
+      </c>
+      <c r="J37" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1574,6 +1802,12 @@
         <v>836992.2512000001</v>
       </c>
       <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>836992.2512000001</v>
+      </c>
+      <c r="J38" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1604,6 +1838,12 @@
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I39" s="4" t="n">
+        <v>834355.5257</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1632,6 +1872,12 @@
       <c r="H40" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I40" s="4" t="n">
+        <v>823353.5943</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1660,6 +1906,12 @@
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I41" s="4" t="n">
+        <v>809555.4168</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1688,6 +1940,12 @@
       <c r="H42" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I42" s="4" t="n">
+        <v>799900.5672</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1716,6 +1974,12 @@
       <c r="H43" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I43" s="4" t="n">
+        <v>763127.9248</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1744,6 +2008,12 @@
       <c r="H44" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I44" s="4" t="n">
+        <v>747868.0344</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1770,6 +2040,12 @@
         <v>732703.1313</v>
       </c>
       <c r="H45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>732703.1313</v>
+      </c>
+      <c r="J45" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1798,6 +2074,12 @@
         <v>725096.5494</v>
       </c>
       <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>725096.5494</v>
+      </c>
+      <c r="J46" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1826,6 +2108,12 @@
         <v>711759.0045</v>
       </c>
       <c r="H47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>711759.0045</v>
+      </c>
+      <c r="J47" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1854,6 +2142,12 @@
         <v>693657.6485</v>
       </c>
       <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>693657.6485</v>
+      </c>
+      <c r="J48" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1882,6 +2176,12 @@
         <v>672356.3260999999</v>
       </c>
       <c r="H49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>672356.3260999999</v>
+      </c>
+      <c r="J49" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1912,6 +2212,12 @@
       <c r="H50" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I50" s="4" t="n">
+        <v>645576.1191</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1938,6 +2244,12 @@
         <v>645051.7397</v>
       </c>
       <c r="H51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>645051.7397</v>
+      </c>
+      <c r="J51" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -1968,6 +2280,12 @@
       <c r="H52" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I52" s="4" t="n">
+        <v>634607.2181000001</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1994,6 +2312,12 @@
         <v>620661.4845</v>
       </c>
       <c r="H53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>620661.4845</v>
+      </c>
+      <c r="J53" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2024,6 +2348,12 @@
       <c r="H54" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I54" s="4" t="n">
+        <v>618815.814</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2052,6 +2382,12 @@
       <c r="H55" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I55" s="4" t="n">
+        <v>577999.0600000001</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2080,6 +2416,12 @@
       <c r="H56" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I56" s="4" t="n">
+        <v>574396.1581</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2108,6 +2450,12 @@
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I57" s="4" t="n">
+        <v>543641.1091999999</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2136,6 +2484,12 @@
       <c r="H58" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I58" s="4" t="n">
+        <v>540799.1483999999</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2164,6 +2518,12 @@
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I59" s="4" t="n">
+        <v>522769.5865</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2190,6 +2550,12 @@
         <v>514620.6938</v>
       </c>
       <c r="H60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>514620.6938</v>
+      </c>
+      <c r="J60" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2218,6 +2584,12 @@
         <v>502486.445</v>
       </c>
       <c r="H61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>502486.445</v>
+      </c>
+      <c r="J61" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2246,6 +2618,12 @@
         <v>500000.0059</v>
       </c>
       <c r="H62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>500000.0059</v>
+      </c>
+      <c r="J62" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2274,6 +2652,12 @@
         <v>496416.2686</v>
       </c>
       <c r="H63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>496416.2686</v>
+      </c>
+      <c r="J63" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2304,6 +2688,12 @@
       <c r="H64" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I64" s="4" t="n">
+        <v>493196.1109</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2332,6 +2722,12 @@
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I65" s="4" t="n">
+        <v>492785.4309</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2360,6 +2756,12 @@
       <c r="H66" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I66" s="4" t="n">
+        <v>485670.7376</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2388,6 +2790,12 @@
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I67" s="4" t="n">
+        <v>479895.4935</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2414,6 +2822,12 @@
         <v>478481.1661</v>
       </c>
       <c r="H68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>478481.1661</v>
+      </c>
+      <c r="J68" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2442,6 +2856,12 @@
         <v>475707.078</v>
       </c>
       <c r="H69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>475707.078</v>
+      </c>
+      <c r="J69" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2472,6 +2892,12 @@
       <c r="H70" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I70" s="4" t="n">
+        <v>464907.3106</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2498,6 +2924,12 @@
         <v>456856.3119</v>
       </c>
       <c r="H71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>456856.3119</v>
+      </c>
+      <c r="J71" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2526,6 +2958,12 @@
         <v>450737.5206</v>
       </c>
       <c r="H72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>450737.5206</v>
+      </c>
+      <c r="J72" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2554,6 +2992,12 @@
         <v>406654.2213</v>
       </c>
       <c r="H73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>406654.2213</v>
+      </c>
+      <c r="J73" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2584,6 +3028,12 @@
       <c r="H74" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I74" s="4" t="n">
+        <v>391965.0651</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2612,6 +3062,12 @@
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I75" s="4" t="n">
+        <v>373610.2211</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2640,6 +3096,12 @@
       <c r="H76" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I76" s="4" t="n">
+        <v>372035.7101</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2668,6 +3130,12 @@
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I77" s="4" t="n">
+        <v>368779.171</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2696,6 +3164,12 @@
       <c r="H78" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I78" s="4" t="n">
+        <v>364313.8869</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2722,6 +3196,12 @@
         <v>349130.2568</v>
       </c>
       <c r="H79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>349130.2568</v>
+      </c>
+      <c r="J79" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2752,6 +3232,12 @@
       <c r="H80" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I80" s="4" t="n">
+        <v>317618.675</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2780,6 +3266,12 @@
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I81" s="4" t="n">
+        <v>306593.6026</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2808,6 +3300,12 @@
       <c r="H82" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I82" s="4" t="n">
+        <v>304779.1145</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2834,6 +3332,12 @@
         <v>279571.178</v>
       </c>
       <c r="H83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>279571.178</v>
+      </c>
+      <c r="J83" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2862,6 +3366,12 @@
         <v>276846.4217</v>
       </c>
       <c r="H84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>276846.4217</v>
+      </c>
+      <c r="J84" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2892,6 +3402,12 @@
       <c r="H85" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I85" s="4" t="n">
+        <v>270452.3185</v>
+      </c>
+      <c r="J85" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2920,6 +3436,12 @@
       <c r="H86" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I86" s="4" t="n">
+        <v>265595.8775</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2948,6 +3470,12 @@
       <c r="H87" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I87" s="4" t="n">
+        <v>262311.5799</v>
+      </c>
+      <c r="J87" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2974,6 +3502,12 @@
         <v>253086.7083</v>
       </c>
       <c r="H88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>253086.7083</v>
+      </c>
+      <c r="J88" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3004,6 +3538,12 @@
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I89" s="4" t="n">
+        <v>248683.7198</v>
+      </c>
+      <c r="J89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3032,6 +3572,12 @@
       <c r="H90" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I90" s="4" t="n">
+        <v>245600</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3060,6 +3606,12 @@
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I91" s="4" t="n">
+        <v>234392.5508</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3088,6 +3640,12 @@
       <c r="H92" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I92" s="4" t="n">
+        <v>232105.4869</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3116,6 +3674,12 @@
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I93" s="4" t="n">
+        <v>232010.2351</v>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3142,6 +3706,12 @@
         <v>210417.5518</v>
       </c>
       <c r="H94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>210417.5518</v>
+      </c>
+      <c r="J94" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3172,6 +3742,12 @@
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I95" s="4" t="n">
+        <v>208196.4767</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3198,6 +3774,12 @@
         <v>200680.3037</v>
       </c>
       <c r="H96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>200680.3037</v>
+      </c>
+      <c r="J96" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3228,6 +3810,12 @@
       <c r="H97" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I97" s="4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3254,6 +3842,12 @@
         <v>193698.4706</v>
       </c>
       <c r="H98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>193698.4706</v>
+      </c>
+      <c r="J98" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3282,6 +3876,12 @@
         <v>189214.5731</v>
       </c>
       <c r="H99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>189214.5731</v>
+      </c>
+      <c r="J99" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3310,6 +3910,12 @@
         <v>184057.6874</v>
       </c>
       <c r="H100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>184057.6874</v>
+      </c>
+      <c r="J100" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3338,6 +3944,12 @@
         <v>179226.4255</v>
       </c>
       <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>179226.4255</v>
+      </c>
+      <c r="J101" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3352,7 +3964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3363,6 +3975,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3406,6 +4020,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>06/08/2026 08:01</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3432,6 +4056,12 @@
         <v>27004519.2645</v>
       </c>
       <c r="H2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>27004519.2645</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3462,6 +4092,12 @@
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I3" s="4" t="n">
+        <v>26470000</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3488,6 +4124,12 @@
         <v>23480366.3071</v>
       </c>
       <c r="H4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>23480366.3071</v>
+      </c>
+      <c r="J4" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3518,6 +4160,12 @@
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="4" t="n">
+        <v>23069630.0654</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3546,6 +4194,12 @@
       <c r="H6" s="7" t="n">
         <v>11672.2089</v>
       </c>
+      <c r="I6" s="4" t="n">
+        <v>22222252.7851</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-374518.9954</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3574,6 +4228,12 @@
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" s="4" t="n">
+        <v>20000000.0069</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3600,6 +4260,12 @@
         <v>18754869.6112</v>
       </c>
       <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>18754869.6112</v>
+      </c>
+      <c r="J8" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3630,6 +4296,12 @@
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I9" s="4" t="n">
+        <v>17900000</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3658,6 +4330,12 @@
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3684,6 +4362,12 @@
         <v>15566890.7147</v>
       </c>
       <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>15566890.7147</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3714,6 +4398,12 @@
       <c r="H12" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I12" s="4" t="n">
+        <v>15077130.0016</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3742,6 +4432,12 @@
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I13" s="4" t="n">
+        <v>14000000.0458</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3770,6 +4466,12 @@
       <c r="H14" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I14" s="4" t="n">
+        <v>13946038.6243</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3798,6 +4500,12 @@
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I15" s="4" t="n">
+        <v>13561030.1654</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3826,6 +4534,12 @@
       <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I16" s="4" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3852,6 +4566,12 @@
         <v>12877042.1771</v>
       </c>
       <c r="H17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>12877042.1771</v>
+      </c>
+      <c r="J17" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3880,6 +4600,12 @@
         <v>12076398.0324</v>
       </c>
       <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>12076398.0324</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3910,6 +4636,12 @@
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I19" s="4" t="n">
+        <v>12035369.0946</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3938,6 +4670,12 @@
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I20" s="4" t="n">
+        <v>11000100</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3964,6 +4702,12 @@
         <v>10537438.7702</v>
       </c>
       <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>10537438.7702</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -3994,6 +4738,12 @@
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I22" s="4" t="n">
+        <v>9100000</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4020,6 +4770,12 @@
         <v>10145020.9338</v>
       </c>
       <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>10145020.9338</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4048,6 +4804,12 @@
         <v>10064319.802</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>10064319.802</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4076,6 +4838,12 @@
         <v>10050792.1674</v>
       </c>
       <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>10050792.1674</v>
+      </c>
+      <c r="J25" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4106,6 +4874,12 @@
       <c r="H26" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I26" s="4" t="n">
+        <v>9974153.375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4132,6 +4906,12 @@
         <v>9950177.2448</v>
       </c>
       <c r="H27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>9950177.2448</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4162,6 +4942,12 @@
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I28" s="4" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4190,6 +4976,12 @@
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I29" s="4" t="n">
+        <v>8928368.352</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4218,6 +5010,12 @@
       <c r="H30" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I30" s="4" t="n">
+        <v>8652441.2765</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4244,6 +5042,12 @@
         <v>8363455.9946</v>
       </c>
       <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>8363455.9946</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4274,6 +5078,12 @@
       <c r="H32" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I32" s="4" t="n">
+        <v>8023815.4821</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4300,6 +5110,12 @@
         <v>8023361.3442</v>
       </c>
       <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>8023361.3442</v>
+      </c>
+      <c r="J33" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4328,6 +5144,12 @@
         <v>8000005.5172</v>
       </c>
       <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>8000005.5172</v>
+      </c>
+      <c r="J34" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4358,6 +5180,12 @@
       <c r="H35" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I35" s="4" t="n">
+        <v>7000187</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4386,6 +5214,12 @@
       <c r="H36" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I36" s="4" t="n">
+        <v>6936249.5374</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4414,6 +5248,12 @@
       <c r="H37" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I37" s="4" t="n">
+        <v>6850000.7835</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4442,6 +5282,12 @@
       <c r="H38" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I38" s="4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4470,6 +5316,12 @@
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I39" s="4" t="n">
+        <v>6434508.4673</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4498,6 +5350,12 @@
       <c r="H40" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I40" s="4" t="n">
+        <v>6157877.2306</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4524,6 +5382,12 @@
         <v>5674606.3075</v>
       </c>
       <c r="H41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>5674606.3075</v>
+      </c>
+      <c r="J41" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4554,6 +5418,12 @@
       <c r="H42" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I42" s="4" t="n">
+        <v>5565141.3215</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4580,6 +5450,12 @@
         <v>5537959.6635</v>
       </c>
       <c r="H43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>5537959.6635</v>
+      </c>
+      <c r="J43" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4608,6 +5484,12 @@
         <v>5443778.7854</v>
       </c>
       <c r="H44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>5443778.7854</v>
+      </c>
+      <c r="J44" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4638,6 +5520,12 @@
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I45" s="4" t="n">
+        <v>5249101.3481</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4666,6 +5554,12 @@
       <c r="H46" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I46" s="4" t="n">
+        <v>5246809.5221</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4694,6 +5588,12 @@
       <c r="H47" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I47" s="4" t="n">
+        <v>5229000</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4722,6 +5622,12 @@
       <c r="H48" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I48" s="4" t="n">
+        <v>5188888.88</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4750,6 +5656,12 @@
       <c r="H49" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I49" s="4" t="n">
+        <v>5003000</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4776,6 +5688,12 @@
         <v>5000000.0018</v>
       </c>
       <c r="H50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>5000000.0018</v>
+      </c>
+      <c r="J50" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -4806,6 +5724,12 @@
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I51" s="4" t="n">
+        <v>4664770.6328</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4832,7 +5756,13 @@
         <v>4614481.0346</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>4229866.0346</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>-384615</v>
       </c>
     </row>
     <row r="53">
@@ -4862,6 +5792,12 @@
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I53" s="4" t="n">
+        <v>4540406.5588</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4890,6 +5826,12 @@
       <c r="H54" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I54" s="4" t="n">
+        <v>4542731.5156</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>5521.3065</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4918,6 +5860,12 @@
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I55" s="4" t="n">
+        <v>5322086.0768</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>800817.2725</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4946,6 +5894,12 @@
       <c r="H56" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I56" s="4" t="n">
+        <v>4519500</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4974,6 +5928,12 @@
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I57" s="4" t="n">
+        <v>4426640.2635</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5002,6 +5962,12 @@
       <c r="H58" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I58" s="4" t="n">
+        <v>4104717.2768</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>39405.1539</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5030,6 +5996,12 @@
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I59" s="4" t="n">
+        <v>4044917.9442</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5058,6 +6030,12 @@
       <c r="H60" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I60" s="4" t="n">
+        <v>4000014.4373</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5084,6 +6062,12 @@
         <v>3927600.0561</v>
       </c>
       <c r="H61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>3927600.0561</v>
+      </c>
+      <c r="J61" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5114,6 +6098,12 @@
       <c r="H62" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I62" s="4" t="n">
+        <v>3891798.8644</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5142,6 +6132,12 @@
       <c r="H63" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I63" s="4" t="n">
+        <v>3806790</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5170,6 +6166,12 @@
       <c r="H64" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I64" s="4" t="n">
+        <v>3777387</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5196,6 +6198,12 @@
         <v>3710432.1672</v>
       </c>
       <c r="H65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>3710432.1672</v>
+      </c>
+      <c r="J65" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5226,6 +6234,12 @@
       <c r="H66" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I66" s="4" t="n">
+        <v>3670420</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5254,6 +6268,12 @@
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I67" s="4" t="n">
+        <v>3651821.6602</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5282,6 +6302,12 @@
       <c r="H68" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I68" s="4" t="n">
+        <v>3579376.119</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5310,6 +6336,12 @@
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I69" s="4" t="n">
+        <v>3534274.8743</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5338,6 +6370,12 @@
       <c r="H70" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I70" s="4" t="n">
+        <v>3500497.764</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5366,6 +6404,12 @@
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I71" s="4" t="n">
+        <v>3487322.2855</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5392,7 +6436,13 @@
         <v>3399453.366</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>4000855.068</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>601401.702</v>
       </c>
     </row>
     <row r="73">
@@ -5422,6 +6472,12 @@
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I73" s="4" t="n">
+        <v>3287999.9796</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5448,6 +6504,12 @@
         <v>3277153.2544</v>
       </c>
       <c r="H74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>3277153.2544</v>
+      </c>
+      <c r="J74" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5478,6 +6540,12 @@
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I75" s="4" t="n">
+        <v>3217781.3694</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5506,6 +6574,12 @@
       <c r="H76" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I76" s="4" t="n">
+        <v>3203353.2229</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5534,6 +6608,12 @@
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I77" s="4" t="n">
+        <v>3148181.9096</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5560,6 +6640,12 @@
         <v>3130293.0222</v>
       </c>
       <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>3130293.0222</v>
+      </c>
+      <c r="J78" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5590,6 +6676,12 @@
       <c r="H79" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I79" s="4" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5618,6 +6710,12 @@
       <c r="H80" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I80" s="4" t="n">
+        <v>3032188.4799</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5646,6 +6744,12 @@
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I81" s="4" t="n">
+        <v>2856916.0402</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5674,6 +6778,12 @@
       <c r="H82" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I82" s="4" t="n">
+        <v>2728360.891</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5700,6 +6810,12 @@
         <v>2646250.8473</v>
       </c>
       <c r="H83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>2646250.8473</v>
+      </c>
+      <c r="J83" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5728,6 +6844,12 @@
         <v>2603698.568</v>
       </c>
       <c r="H84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>2603698.568</v>
+      </c>
+      <c r="J84" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5756,7 +6878,13 @@
         <v>2585748.6673</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>2596928.8122</v>
+      </c>
+      <c r="J85" s="7" t="n">
+        <v>11180.1449</v>
       </c>
     </row>
     <row r="86">
@@ -5786,6 +6914,12 @@
       <c r="H86" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I86" s="4" t="n">
+        <v>2578757.6772</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5812,6 +6946,12 @@
         <v>2566060.4818</v>
       </c>
       <c r="H87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>2566060.4818</v>
+      </c>
+      <c r="J87" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5842,6 +6982,12 @@
       <c r="H88" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="I88" s="4" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5870,6 +7016,12 @@
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I89" s="4" t="n">
+        <v>2489000.3733</v>
+      </c>
+      <c r="J89" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5898,6 +7050,12 @@
       <c r="H90" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I90" s="4" t="n">
+        <v>2470041.0495</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5926,6 +7084,12 @@
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I91" s="4" t="n">
+        <v>2411374.8288</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5952,6 +7116,12 @@
         <v>2384406.6695</v>
       </c>
       <c r="H92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>2384406.6695</v>
+      </c>
+      <c r="J92" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -5982,6 +7152,12 @@
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I93" s="4" t="n">
+        <v>2370068.8696</v>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6010,6 +7186,12 @@
       <c r="H94" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I94" s="4" t="n">
+        <v>2361819.476</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6036,6 +7218,12 @@
         <v>2335954.4783</v>
       </c>
       <c r="H95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>2335954.4783</v>
+      </c>
+      <c r="J95" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6064,6 +7252,12 @@
         <v>2289568.431</v>
       </c>
       <c r="H96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>2289568.431</v>
+      </c>
+      <c r="J96" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6092,6 +7286,12 @@
         <v>2275539.2648</v>
       </c>
       <c r="H97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>2275539.2648</v>
+      </c>
+      <c r="J97" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6122,6 +7322,12 @@
       <c r="H98" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I98" s="4" t="n">
+        <v>2264858.6935</v>
+      </c>
+      <c r="J98" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6150,6 +7356,12 @@
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I99" s="4" t="n">
+        <v>2263684.8207</v>
+      </c>
+      <c r="J99" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6176,6 +7388,12 @@
         <v>2227988.9889</v>
       </c>
       <c r="H100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>2227988.9889</v>
+      </c>
+      <c r="J100" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6204,6 +7422,12 @@
         <v>2203811.7904</v>
       </c>
       <c r="H101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>2203811.7904</v>
+      </c>
+      <c r="J101" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6218,13 +7442,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6248,6 +7474,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>06/08/2026 08:01</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6264,6 +7500,12 @@
         <v>30520979.1924</v>
       </c>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>30520979.1924</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6280,6 +7522,12 @@
         <v>28485323.9097</v>
       </c>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>28485323.9097</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6296,6 +7544,12 @@
         <v>20000000</v>
       </c>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -6312,6 +7566,12 @@
         <v>14808642.0248</v>
       </c>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>14808642.0248</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -6328,6 +7588,12 @@
         <v>13955655.1909</v>
       </c>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>13955655.1909</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6344,6 +7610,12 @@
         <v>13650572.8907</v>
       </c>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>13665606.3839</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>15033.4932</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6360,6 +7632,12 @@
         <v>13363396.9665</v>
       </c>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>13363396.9665</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6376,6 +7654,12 @@
         <v>13055036.4516</v>
       </c>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>13055036.4516</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -6392,6 +7676,12 @@
         <v>11877969.9425</v>
       </c>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>11877969.9425</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -6408,6 +7698,12 @@
         <v>10950000.9992</v>
       </c>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>10950000.9992</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6424,6 +7720,12 @@
         <v>10497910.9711</v>
       </c>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>10497910.9711</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -6440,6 +7742,12 @@
         <v>10466354.1133</v>
       </c>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>10466354.1133</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -6456,6 +7764,12 @@
         <v>10000352.735</v>
       </c>
       <c r="D14" s="5" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>10000352.735</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -6472,6 +7786,12 @@
         <v>9703974.7772</v>
       </c>
       <c r="D15" s="5" t="n"/>
+      <c r="E15" s="4" t="n">
+        <v>9703974.7772</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -6488,6 +7808,12 @@
         <v>9081000.1829</v>
       </c>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="4" t="n">
+        <v>9081000.1829</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -6504,6 +7830,12 @@
         <v>9045888.3857</v>
       </c>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>9045888.3857</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6520,6 +7852,12 @@
         <v>8722578.914100001</v>
       </c>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>8733265.484999999</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>10686.5709</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -6536,6 +7874,12 @@
         <v>8711385</v>
       </c>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>8711385</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -6552,6 +7896,12 @@
         <v>8651347.4691</v>
       </c>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="4" t="n">
+        <v>8651347.4691</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -6568,6 +7918,12 @@
         <v>8401023.438300001</v>
       </c>
       <c r="D21" s="5" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>8401023.438300001</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -6584,6 +7940,12 @@
         <v>7904138.1249</v>
       </c>
       <c r="D22" s="5" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>7904138.1249</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -6600,6 +7962,12 @@
         <v>7753623.1938</v>
       </c>
       <c r="D23" s="5" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>7753623.1938</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -6616,6 +7984,12 @@
         <v>7445008.5622</v>
       </c>
       <c r="D24" s="5" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>7445008.5622</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -6632,6 +8006,12 @@
         <v>7229423.4285</v>
       </c>
       <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n">
+        <v>7229423.4285</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -6648,6 +8028,12 @@
         <v>7124816.6694</v>
       </c>
       <c r="D26" s="5" t="n"/>
+      <c r="E26" s="4" t="n">
+        <v>7124816.6694</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6664,6 +8050,12 @@
         <v>6904270.1775</v>
       </c>
       <c r="D27" s="5" t="n"/>
+      <c r="E27" s="4" t="n">
+        <v>6904270.1775</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -6680,6 +8072,12 @@
         <v>6847950.1462</v>
       </c>
       <c r="D28" s="5" t="n"/>
+      <c r="E28" s="4" t="n">
+        <v>6845460.3847</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-2489.7615</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6696,6 +8094,12 @@
         <v>6836034.0034</v>
       </c>
       <c r="D29" s="5" t="n"/>
+      <c r="E29" s="4" t="n">
+        <v>6966050.5548</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>130016.5514</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6712,6 +8116,12 @@
         <v>6574441.9423</v>
       </c>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="4" t="n">
+        <v>6574441.9423</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6728,6 +8138,12 @@
         <v>6500000</v>
       </c>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6744,6 +8160,12 @@
         <v>6148640.0548</v>
       </c>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="4" t="n">
+        <v>6148640.0548</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6760,6 +8182,12 @@
         <v>6116138.8294</v>
       </c>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="4" t="n">
+        <v>6116138.8294</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6776,6 +8204,12 @@
         <v>5989650.4407</v>
       </c>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="4" t="n">
+        <v>5989650.4407</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6792,6 +8226,12 @@
         <v>5913624.5861</v>
       </c>
       <c r="D35" s="5" t="n"/>
+      <c r="E35" s="4" t="n">
+        <v>5913624.5861</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6808,6 +8248,12 @@
         <v>5745360.968</v>
       </c>
       <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="n">
+        <v>5745360.968</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6824,6 +8270,12 @@
         <v>5560234.6103</v>
       </c>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="n">
+        <v>5560234.6103</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6840,6 +8292,12 @@
         <v>5213528.6062</v>
       </c>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="4" t="n">
+        <v>5213528.6062</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6856,6 +8314,12 @@
         <v>4734322.9228</v>
       </c>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="4" t="n">
+        <v>4734322.9228</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6872,6 +8336,12 @@
         <v>4683092.749</v>
       </c>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n">
+        <v>4683092.749</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6888,6 +8358,12 @@
         <v>4611862.884</v>
       </c>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n">
+        <v>4611862.884</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6904,6 +8380,12 @@
         <v>4393891.0983</v>
       </c>
       <c r="D42" s="5" t="n"/>
+      <c r="E42" s="4" t="n">
+        <v>4393891.0983</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -6920,6 +8402,12 @@
         <v>4368320.2419</v>
       </c>
       <c r="D43" s="5" t="n"/>
+      <c r="E43" s="4" t="n">
+        <v>4368320.2419</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6936,6 +8424,12 @@
         <v>4283944.4597</v>
       </c>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="4" t="n">
+        <v>4283944.4597</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -6952,6 +8446,12 @@
         <v>4283680.8613</v>
       </c>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="4" t="n">
+        <v>4283680.8613</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -6968,6 +8468,12 @@
         <v>4263304.9862</v>
       </c>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="n">
+        <v>4263304.9862</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -6984,6 +8490,12 @@
         <v>4232810.3687</v>
       </c>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="n">
+        <v>4232810.3687</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -7000,6 +8512,12 @@
         <v>4155860.0882</v>
       </c>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="4" t="n">
+        <v>4155860.0882</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -7016,6 +8534,12 @@
         <v>4129406.5164</v>
       </c>
       <c r="D49" s="5" t="n"/>
+      <c r="E49" s="4" t="n">
+        <v>4129406.5164</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -7032,6 +8556,12 @@
         <v>4125367</v>
       </c>
       <c r="D50" s="5" t="n"/>
+      <c r="E50" s="4" t="n">
+        <v>4125367</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -7048,6 +8578,12 @@
         <v>4001000.0311</v>
       </c>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n">
+        <v>4001000.0311</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -7064,6 +8600,12 @@
         <v>4000000</v>
       </c>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -7080,6 +8622,12 @@
         <v>3905978.0445</v>
       </c>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="4" t="n">
+        <v>3905978.0445</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -7096,6 +8644,12 @@
         <v>3900000.6952</v>
       </c>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="4" t="n">
+        <v>3900000.6952</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -7112,6 +8666,12 @@
         <v>3660840.1514</v>
       </c>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="4" t="n">
+        <v>3660840.1514</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -7128,6 +8688,12 @@
         <v>3600815.2143</v>
       </c>
       <c r="D56" s="5" t="n"/>
+      <c r="E56" s="4" t="n">
+        <v>3600815.2143</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -7144,6 +8710,12 @@
         <v>3521971.5871</v>
       </c>
       <c r="D57" s="5" t="n"/>
+      <c r="E57" s="4" t="n">
+        <v>3521971.5871</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7160,6 +8732,12 @@
         <v>3500100</v>
       </c>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="4" t="n">
+        <v>3500100</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -7176,6 +8754,12 @@
         <v>3483829.0767</v>
       </c>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="4" t="n">
+        <v>3483829.0767</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7192,6 +8776,12 @@
         <v>3394243.2595</v>
       </c>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="4" t="n">
+        <v>3394243.2595</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -7208,6 +8798,12 @@
         <v>3383497.4498</v>
       </c>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="4" t="n">
+        <v>3383497.4498</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -7224,6 +8820,12 @@
         <v>3368404.471</v>
       </c>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="4" t="n">
+        <v>3368404.471</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7240,6 +8842,12 @@
         <v>3245658.8196</v>
       </c>
       <c r="D63" s="5" t="n"/>
+      <c r="E63" s="4" t="n">
+        <v>3245658.8196</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -7256,6 +8864,12 @@
         <v>3140000</v>
       </c>
       <c r="D64" s="5" t="n"/>
+      <c r="E64" s="4" t="n">
+        <v>3140000</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -7272,6 +8886,12 @@
         <v>3137170.579</v>
       </c>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="4" t="n">
+        <v>3137170.579</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -7288,6 +8908,12 @@
         <v>3123654</v>
       </c>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>3123654</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -7304,6 +8930,12 @@
         <v>3091319.0383</v>
       </c>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="4" t="n">
+        <v>3091319.0383</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7320,6 +8952,12 @@
         <v>3072698.763</v>
       </c>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="4" t="n">
+        <v>3072698.763</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -7336,6 +8974,12 @@
         <v>3000000</v>
       </c>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7352,6 +8996,12 @@
         <v>3000000</v>
       </c>
       <c r="D70" s="5" t="n"/>
+      <c r="E70" s="4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7368,6 +9018,12 @@
         <v>2973872.3136</v>
       </c>
       <c r="D71" s="5" t="n"/>
+      <c r="E71" s="4" t="n">
+        <v>2973872.3136</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7384,6 +9040,12 @@
         <v>2950633.646</v>
       </c>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="4" t="n">
+        <v>2950633.646</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -7400,6 +9062,12 @@
         <v>2909500.9876</v>
       </c>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="4" t="n">
+        <v>2909500.9876</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7416,6 +9084,12 @@
         <v>2891843.2925</v>
       </c>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="4" t="n">
+        <v>2891843.2925</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7432,6 +9106,12 @@
         <v>2881207.2314</v>
       </c>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="4" t="n">
+        <v>2881207.2314</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7448,6 +9128,12 @@
         <v>2840623.0813</v>
       </c>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="4" t="n">
+        <v>2840623.0813</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7464,6 +9150,12 @@
         <v>2807640.3471</v>
       </c>
       <c r="D77" s="5" t="n"/>
+      <c r="E77" s="4" t="n">
+        <v>2807640.3471</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7480,6 +9172,12 @@
         <v>2788208.7317</v>
       </c>
       <c r="D78" s="5" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>2788208.7317</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7496,6 +9194,12 @@
         <v>2745744</v>
       </c>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>2745744</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7512,6 +9216,12 @@
         <v>2700000.1965</v>
       </c>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="4" t="n">
+        <v>2700000.1965</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -7528,6 +9238,12 @@
         <v>2606056.9299</v>
       </c>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>2606056.9299</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7544,6 +9260,12 @@
         <v>2581406.1876</v>
       </c>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>2581406.1876</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7560,6 +9282,12 @@
         <v>2574029.367</v>
       </c>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="4" t="n">
+        <v>2574029.367</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7576,6 +9304,12 @@
         <v>2558018.4975</v>
       </c>
       <c r="D84" s="5" t="n"/>
+      <c r="E84" s="4" t="n">
+        <v>2558018.4975</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7592,6 +9326,12 @@
         <v>2514361.2647</v>
       </c>
       <c r="D85" s="5" t="n"/>
+      <c r="E85" s="4" t="n">
+        <v>2514361.2647</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7608,6 +9348,12 @@
         <v>2433024</v>
       </c>
       <c r="D86" s="5" t="n"/>
+      <c r="E86" s="4" t="n">
+        <v>2433024</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7624,6 +9370,12 @@
         <v>2419271.9384</v>
       </c>
       <c r="D87" s="5" t="n"/>
+      <c r="E87" s="4" t="n">
+        <v>2419271.9384</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7640,6 +9392,12 @@
         <v>2403417.0469</v>
       </c>
       <c r="D88" s="5" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>2403417.0469</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7656,6 +9414,12 @@
         <v>2390187.2657</v>
       </c>
       <c r="D89" s="5" t="n"/>
+      <c r="E89" s="4" t="n">
+        <v>2390187.2657</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7672,6 +9436,12 @@
         <v>2355571.632</v>
       </c>
       <c r="D90" s="5" t="n"/>
+      <c r="E90" s="4" t="n">
+        <v>2355571.632</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -7688,6 +9458,12 @@
         <v>2344726.8593</v>
       </c>
       <c r="D91" s="5" t="n"/>
+      <c r="E91" s="4" t="n">
+        <v>2344726.8593</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7704,6 +9480,12 @@
         <v>2300000.5926</v>
       </c>
       <c r="D92" s="5" t="n"/>
+      <c r="E92" s="4" t="n">
+        <v>2300000.5926</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7720,6 +9502,12 @@
         <v>2278552.7571</v>
       </c>
       <c r="D93" s="5" t="n"/>
+      <c r="E93" s="4" t="n">
+        <v>2278552.7571</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7736,6 +9524,12 @@
         <v>2274832.8859</v>
       </c>
       <c r="D94" s="5" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>2274832.8859</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7752,6 +9546,12 @@
         <v>2268074.3017</v>
       </c>
       <c r="D95" s="5" t="n"/>
+      <c r="E95" s="4" t="n">
+        <v>2268074.3017</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7768,6 +9568,12 @@
         <v>2223000</v>
       </c>
       <c r="D96" s="5" t="n"/>
+      <c r="E96" s="4" t="n">
+        <v>2177000</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>-46000</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7784,6 +9590,12 @@
         <v>2214975.5538</v>
       </c>
       <c r="D97" s="5" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>2214975.5538</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7800,6 +9612,12 @@
         <v>2181764.0737</v>
       </c>
       <c r="D98" s="5" t="n"/>
+      <c r="E98" s="4" t="n">
+        <v>2181764.0737</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7816,6 +9634,12 @@
         <v>2169709.2706</v>
       </c>
       <c r="D99" s="5" t="n"/>
+      <c r="E99" s="4" t="n">
+        <v>2169709.2706</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7832,6 +9656,12 @@
         <v>2071580.1255</v>
       </c>
       <c r="D100" s="5" t="n"/>
+      <c r="E100" s="4" t="n">
+        <v>2071580.1255</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7848,6 +9678,12 @@
         <v>2038371.3021</v>
       </c>
       <c r="D101" s="5" t="n"/>
+      <c r="E101" s="4" t="n">
+        <v>2038371.3021</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7860,13 +9696,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7890,6 +9728,16 @@
           <t>Chênh lệch</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>06/08/2026 08:01</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Chênh lệch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7906,6 +9754,12 @@
         <v>4976700.4092</v>
       </c>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="4" t="n">
+        <v>5001643.0337</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>24942.6245</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7922,6 +9776,12 @@
         <v>2313347.1807</v>
       </c>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>2365565.9494</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>52218.7687</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7938,6 +9798,12 @@
         <v>2214286.191</v>
       </c>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>2214286.191</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7954,6 +9820,12 @@
         <v>2106038.2213</v>
       </c>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>2291076.8834</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>185038.6621</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7970,6 +9842,12 @@
         <v>1172275.1874</v>
       </c>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>1172275.1874</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7986,6 +9864,12 @@
         <v>1053611.1676</v>
       </c>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>1053611.1676</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8002,6 +9886,12 @@
         <v>1046924.3234</v>
       </c>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="4" t="n">
+        <v>1046924.3234</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8018,6 +9908,12 @@
         <v>1019712.413</v>
       </c>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>1019712.413</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8034,6 +9930,12 @@
         <v>1000000</v>
       </c>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8050,6 +9952,12 @@
         <v>897950.7675</v>
       </c>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>897950.7675</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8066,6 +9974,12 @@
         <v>823887.4096</v>
       </c>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="4" t="n">
+        <v>823887.4096</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8082,6 +9996,12 @@
         <v>777000.2937</v>
       </c>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="4" t="n">
+        <v>777000.2937</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8098,6 +10018,12 @@
         <v>750000.001</v>
       </c>
       <c r="D14" s="5" t="n"/>
+      <c r="E14" s="4" t="n">
+        <v>750000.001</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8114,6 +10040,12 @@
         <v>750000.001</v>
       </c>
       <c r="D15" s="5" t="n"/>
+      <c r="E15" s="4" t="n">
+        <v>750000.001</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8130,6 +10062,12 @@
         <v>700000.231</v>
       </c>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="4" t="n">
+        <v>700000.231</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -8146,6 +10084,12 @@
         <v>686827.8777</v>
       </c>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="4" t="n">
+        <v>681070.1265</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-5757.7512</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8162,6 +10106,12 @@
         <v>627640.3759</v>
       </c>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>627640.3759</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8178,6 +10128,12 @@
         <v>599513.0695</v>
       </c>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>599513.0695</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8194,6 +10150,12 @@
         <v>588698.001</v>
       </c>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="4" t="n">
+        <v>588698.001</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8210,6 +10172,12 @@
         <v>570000.4782</v>
       </c>
       <c r="D21" s="5" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>570000.4782</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8226,6 +10194,12 @@
         <v>545239.751</v>
       </c>
       <c r="D22" s="5" t="n"/>
+      <c r="E22" s="4" t="n">
+        <v>545239.751</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8242,6 +10216,12 @@
         <v>539889.8815</v>
       </c>
       <c r="D23" s="5" t="n"/>
+      <c r="E23" s="4" t="n">
+        <v>539889.8815</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -8258,6 +10238,12 @@
         <v>523466.0617</v>
       </c>
       <c r="D24" s="5" t="n"/>
+      <c r="E24" s="4" t="n">
+        <v>523466.0617</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -8274,6 +10260,12 @@
         <v>521487.3899</v>
       </c>
       <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n">
+        <v>521487.3899</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8290,6 +10282,12 @@
         <v>501931.2321</v>
       </c>
       <c r="D26" s="5" t="n"/>
+      <c r="E26" s="4" t="n">
+        <v>501931.2321</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -8306,6 +10304,12 @@
         <v>498061.7132</v>
       </c>
       <c r="D27" s="5" t="n"/>
+      <c r="E27" s="4" t="n">
+        <v>498061.7132</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -8322,6 +10326,12 @@
         <v>470548.7919</v>
       </c>
       <c r="D28" s="5" t="n"/>
+      <c r="E28" s="4" t="n">
+        <v>470548.7919</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -8338,6 +10348,12 @@
         <v>450108.8158</v>
       </c>
       <c r="D29" s="5" t="n"/>
+      <c r="E29" s="4" t="n">
+        <v>450108.8158</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8354,6 +10370,12 @@
         <v>415714.3805</v>
       </c>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="4" t="n">
+        <v>415714.3805</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8370,6 +10392,12 @@
         <v>408223.1085</v>
       </c>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="4" t="n">
+        <v>408223.1085</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8386,6 +10414,12 @@
         <v>400238.9755</v>
       </c>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="4" t="n">
+        <v>400238.9755</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -8402,6 +10436,12 @@
         <v>370000.8927</v>
       </c>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="4" t="n">
+        <v>370000.8927</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8418,6 +10458,12 @@
         <v>356213.8346</v>
       </c>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="4" t="n">
+        <v>356213.8346</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -8434,6 +10480,12 @@
         <v>348972.7294</v>
       </c>
       <c r="D35" s="5" t="n"/>
+      <c r="E35" s="4" t="n">
+        <v>348972.7294</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -8450,6 +10502,12 @@
         <v>344999.7763</v>
       </c>
       <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="n">
+        <v>344999.7763</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -8466,6 +10524,12 @@
         <v>343179.1316</v>
       </c>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="n">
+        <v>343179.1316</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -8482,6 +10546,12 @@
         <v>326484.5328</v>
       </c>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="4" t="n">
+        <v>326484.5328</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -8498,6 +10568,12 @@
         <v>326060.7935</v>
       </c>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="4" t="n">
+        <v>326060.7935</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8514,6 +10590,12 @@
         <v>306577.9649</v>
       </c>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n">
+        <v>306577.9649</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8530,6 +10612,12 @@
         <v>295536.9332</v>
       </c>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n">
+        <v>295536.9332</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8546,6 +10634,12 @@
         <v>293786.1018</v>
       </c>
       <c r="D42" s="5" t="n"/>
+      <c r="E42" s="4" t="n">
+        <v>293786.1018</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8562,6 +10656,12 @@
         <v>285000.001</v>
       </c>
       <c r="D43" s="5" t="n"/>
+      <c r="E43" s="4" t="n">
+        <v>285000.001</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8578,6 +10678,12 @@
         <v>281629.4939</v>
       </c>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="4" t="n">
+        <v>281629.4939</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8594,6 +10700,12 @@
         <v>271817.0389</v>
       </c>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="4" t="n">
+        <v>271817.0389</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8610,6 +10722,12 @@
         <v>267461.4365</v>
       </c>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="n">
+        <v>267461.4365</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8626,6 +10744,12 @@
         <v>264414.4323</v>
       </c>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="n">
+        <v>264414.4323</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8642,6 +10766,12 @@
         <v>253677.9782</v>
       </c>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="4" t="n">
+        <v>253677.9782</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -8658,6 +10788,12 @@
         <v>251513.5263</v>
       </c>
       <c r="D49" s="5" t="n"/>
+      <c r="E49" s="4" t="n">
+        <v>251513.5263</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8674,6 +10810,12 @@
         <v>243482.9412</v>
       </c>
       <c r="D50" s="5" t="n"/>
+      <c r="E50" s="4" t="n">
+        <v>243482.9412</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -8690,6 +10832,12 @@
         <v>241310.5368</v>
       </c>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n">
+        <v>241310.5368</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -8706,6 +10854,12 @@
         <v>240561.9116</v>
       </c>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>240561.9116</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8722,6 +10876,12 @@
         <v>236974.746</v>
       </c>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="4" t="n">
+        <v>236974.746</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8738,6 +10898,12 @@
         <v>233629.5261</v>
       </c>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="4" t="n">
+        <v>233629.5261</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -8754,6 +10920,12 @@
         <v>231622.8616</v>
       </c>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="4" t="n">
+        <v>231622.8616</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -8770,6 +10942,12 @@
         <v>222266.5693</v>
       </c>
       <c r="D56" s="5" t="n"/>
+      <c r="E56" s="4" t="n">
+        <v>222266.5693</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -8786,6 +10964,12 @@
         <v>217465.3479</v>
       </c>
       <c r="D57" s="5" t="n"/>
+      <c r="E57" s="4" t="n">
+        <v>217465.3479</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -8802,6 +10986,12 @@
         <v>216566.8413</v>
       </c>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="4" t="n">
+        <v>216566.8413</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -8818,6 +11008,12 @@
         <v>212280.9443</v>
       </c>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="4" t="n">
+        <v>212280.9443</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -8834,6 +11030,12 @@
         <v>211426.2168</v>
       </c>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="4" t="n">
+        <v>211426.2168</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -8850,6 +11052,12 @@
         <v>206815.5368</v>
       </c>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="4" t="n">
+        <v>206815.5368</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8866,6 +11074,12 @@
         <v>202410.95</v>
       </c>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="4" t="n">
+        <v>202410.95</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -8882,6 +11096,12 @@
         <v>200460.2851</v>
       </c>
       <c r="D63" s="5" t="n"/>
+      <c r="E63" s="4" t="n">
+        <v>200460.2851</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8898,6 +11118,12 @@
         <v>200366.4286</v>
       </c>
       <c r="D64" s="5" t="n"/>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>-200366.4286</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -8914,6 +11140,12 @@
         <v>200100.0027</v>
       </c>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="4" t="n">
+        <v>200100.0027</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8930,6 +11162,12 @@
         <v>200000.003</v>
       </c>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="4" t="n">
+        <v>200000.003</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8946,6 +11184,12 @@
         <v>199229.0666</v>
       </c>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="4" t="n">
+        <v>199229.0666</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8962,6 +11206,12 @@
         <v>193403.8264</v>
       </c>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="4" t="n">
+        <v>193403.8264</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8978,6 +11228,12 @@
         <v>190133.681</v>
       </c>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="4" t="n">
+        <v>190133.681</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8994,6 +11250,12 @@
         <v>185707.0997</v>
       </c>
       <c r="D70" s="5" t="n"/>
+      <c r="E70" s="4" t="n">
+        <v>185707.0997</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -9010,6 +11272,12 @@
         <v>169133.0666</v>
       </c>
       <c r="D71" s="5" t="n"/>
+      <c r="E71" s="4" t="n">
+        <v>169133.0666</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -9026,6 +11294,12 @@
         <v>166366.5773</v>
       </c>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="4" t="n">
+        <v>166366.5773</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -9042,6 +11316,12 @@
         <v>162771.4522</v>
       </c>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="4" t="n">
+        <v>162771.4522</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -9058,6 +11338,12 @@
         <v>158819.0758</v>
       </c>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="4" t="n">
+        <v>158819.0758</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -9074,6 +11360,12 @@
         <v>158686.0651</v>
       </c>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="4" t="n">
+        <v>158686.0651</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -9090,6 +11382,12 @@
         <v>156656.8749</v>
       </c>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="4" t="n">
+        <v>156656.8749</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9106,6 +11404,12 @@
         <v>155914.8696</v>
       </c>
       <c r="D77" s="5" t="n"/>
+      <c r="E77" s="4" t="n">
+        <v>155914.8696</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9122,6 +11426,12 @@
         <v>154759.2409</v>
       </c>
       <c r="D78" s="5" t="n"/>
+      <c r="E78" s="4" t="n">
+        <v>154759.2409</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -9138,6 +11448,12 @@
         <v>153035.4628</v>
       </c>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="4" t="n">
+        <v>153035.4628</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9154,6 +11470,12 @@
         <v>151610.9121</v>
       </c>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="4" t="n">
+        <v>151610.9121</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -9170,6 +11492,12 @@
         <v>151424.8522</v>
       </c>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="4" t="n">
+        <v>151424.8522</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -9186,6 +11514,12 @@
         <v>150487.8467</v>
       </c>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="4" t="n">
+        <v>150487.8467</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -9202,6 +11536,12 @@
         <v>150302.4017</v>
       </c>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="4" t="n">
+        <v>150302.4017</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -9218,6 +11558,12 @@
         <v>150036.9878</v>
       </c>
       <c r="D84" s="5" t="n"/>
+      <c r="E84" s="4" t="n">
+        <v>150036.9878</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -9234,6 +11580,12 @@
         <v>150000.6498</v>
       </c>
       <c r="D85" s="5" t="n"/>
+      <c r="E85" s="4" t="n">
+        <v>150000.6498</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -9250,6 +11602,12 @@
         <v>150000.001</v>
       </c>
       <c r="D86" s="5" t="n"/>
+      <c r="E86" s="4" t="n">
+        <v>150000.001</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -9266,6 +11624,12 @@
         <v>149900.0082</v>
       </c>
       <c r="D87" s="5" t="n"/>
+      <c r="E87" s="4" t="n">
+        <v>149900.0082</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -9282,6 +11646,12 @@
         <v>147428.1548</v>
       </c>
       <c r="D88" s="5" t="n"/>
+      <c r="E88" s="4" t="n">
+        <v>147428.1548</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -9298,6 +11668,12 @@
         <v>146885.6077</v>
       </c>
       <c r="D89" s="5" t="n"/>
+      <c r="E89" s="4" t="n">
+        <v>146885.6077</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -9314,6 +11690,12 @@
         <v>146758.535</v>
       </c>
       <c r="D90" s="5" t="n"/>
+      <c r="E90" s="4" t="n">
+        <v>146758.535</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9330,6 +11712,12 @@
         <v>146641.7138</v>
       </c>
       <c r="D91" s="5" t="n"/>
+      <c r="E91" s="4" t="n">
+        <v>146641.7138</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9346,6 +11734,12 @@
         <v>146516.2953</v>
       </c>
       <c r="D92" s="5" t="n"/>
+      <c r="E92" s="4" t="n">
+        <v>153200.2132</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>6683.9179</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9362,6 +11756,12 @@
         <v>146113.5092</v>
       </c>
       <c r="D93" s="5" t="n"/>
+      <c r="E93" s="4" t="n">
+        <v>146113.5092</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9378,6 +11778,12 @@
         <v>145794.0494</v>
       </c>
       <c r="D94" s="5" t="n"/>
+      <c r="E94" s="4" t="n">
+        <v>145794.0494</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9394,6 +11800,12 @@
         <v>145000.001</v>
       </c>
       <c r="D95" s="5" t="n"/>
+      <c r="E95" s="4" t="n">
+        <v>145000.001</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9410,6 +11822,12 @@
         <v>142277.791</v>
       </c>
       <c r="D96" s="5" t="n"/>
+      <c r="E96" s="4" t="n">
+        <v>142277.791</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9426,6 +11844,12 @@
         <v>137164.0534</v>
       </c>
       <c r="D97" s="5" t="n"/>
+      <c r="E97" s="4" t="n">
+        <v>137164.0534</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9442,6 +11866,12 @@
         <v>137000.6095</v>
       </c>
       <c r="D98" s="5" t="n"/>
+      <c r="E98" s="4" t="n">
+        <v>137000.6095</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9458,6 +11888,12 @@
         <v>136857.5203</v>
       </c>
       <c r="D99" s="5" t="n"/>
+      <c r="E99" s="4" t="n">
+        <v>136857.5203</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9474,6 +11910,12 @@
         <v>134975.955</v>
       </c>
       <c r="D100" s="5" t="n"/>
+      <c r="E100" s="4" t="n">
+        <v>134975.955</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -9490,6 +11932,28 @@
         <v>132924.65</v>
       </c>
       <c r="D101" s="5" t="n"/>
+      <c r="E101" s="4" t="n">
+        <v>132924.65</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>0:149d189061f6c3e90da44ca5a61a824b521fa5a372baef1e448b333d620e3260</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>REDO</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>132757.1085</v>
+      </c>
+      <c r="F102" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
